--- a/MaestraPLU_Carniceria.xlsx
+++ b/MaestraPLU_Carniceria.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F343"/>
+  <dimension ref="A1:F341"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -5161,19 +5161,19 @@
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>401352</v>
+        <v>401701</v>
       </c>
       <c r="B239" t="str">
-        <v>V.COGOTE VACUNO</v>
+        <v>NOVILLO EN PIE KILO</v>
       </c>
       <c r="C239" t="str">
         <v/>
       </c>
       <c r="D239" t="str">
-        <v>1352</v>
+        <v>1701</v>
       </c>
       <c r="E239" t="str">
-        <v>12000</v>
+        <v>2850</v>
       </c>
       <c r="F239" t="str">
         <v>Por peso</v>
@@ -5181,19 +5181,19 @@
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>401701</v>
+        <v>401702</v>
       </c>
       <c r="B240" t="str">
-        <v>NOVILLO EN PIE KILO</v>
+        <v>NOVILLO EN PIE</v>
       </c>
       <c r="C240" t="str">
         <v/>
       </c>
       <c r="D240" t="str">
-        <v>1701</v>
+        <v>1702</v>
       </c>
       <c r="E240" t="str">
-        <v>2850</v>
+        <v>2100</v>
       </c>
       <c r="F240" t="str">
         <v>Por peso</v>
@@ -5201,19 +5201,19 @@
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>401702</v>
+        <v>401705</v>
       </c>
       <c r="B241" t="str">
-        <v>NOVILLO EN PIE</v>
+        <v>FILETE DE EQUINO KILO</v>
       </c>
       <c r="C241" t="str">
         <v/>
       </c>
       <c r="D241" t="str">
-        <v>1702</v>
+        <v>1705</v>
       </c>
       <c r="E241" t="str">
-        <v>2100</v>
+        <v>11790</v>
       </c>
       <c r="F241" t="str">
         <v>Por peso</v>
@@ -5221,19 +5221,19 @@
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>401705</v>
+        <v>401706</v>
       </c>
       <c r="B242" t="str">
-        <v>FILETE DE EQUINO KILO</v>
+        <v>LOMO LISO EQUINO KG.</v>
       </c>
       <c r="C242" t="str">
         <v/>
       </c>
       <c r="D242" t="str">
-        <v>1705</v>
+        <v>1706</v>
       </c>
       <c r="E242" t="str">
-        <v>11790</v>
+        <v>11490</v>
       </c>
       <c r="F242" t="str">
         <v>Por peso</v>
@@ -5241,19 +5241,19 @@
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>401706</v>
+        <v>401707</v>
       </c>
       <c r="B243" t="str">
-        <v>LOMO LISO EQUINO KG.</v>
+        <v>ASIENTO EQUINO KG.</v>
       </c>
       <c r="C243" t="str">
         <v/>
       </c>
       <c r="D243" t="str">
-        <v>1706</v>
+        <v>1707</v>
       </c>
       <c r="E243" t="str">
-        <v>11490</v>
+        <v>9990</v>
       </c>
       <c r="F243" t="str">
         <v>Por peso</v>
@@ -5261,19 +5261,19 @@
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>401707</v>
+        <v>401708</v>
       </c>
       <c r="B244" t="str">
-        <v>ASIENTO EQUINO KG.</v>
+        <v>PUNTA PICANA EQUINO KG.</v>
       </c>
       <c r="C244" t="str">
         <v/>
       </c>
       <c r="D244" t="str">
-        <v>1707</v>
+        <v>1708</v>
       </c>
       <c r="E244" t="str">
-        <v>9990</v>
+        <v>7990</v>
       </c>
       <c r="F244" t="str">
         <v>Por peso</v>
@@ -5281,19 +5281,19 @@
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>401708</v>
+        <v>401709</v>
       </c>
       <c r="B245" t="str">
-        <v>PUNTA PICANA EQUINO KG.</v>
+        <v>POLLO GANSO EQUINO KG.</v>
       </c>
       <c r="C245" t="str">
         <v/>
       </c>
       <c r="D245" t="str">
-        <v>1708</v>
+        <v>1709</v>
       </c>
       <c r="E245" t="str">
-        <v>7990</v>
+        <v>8290</v>
       </c>
       <c r="F245" t="str">
         <v>Por peso</v>
@@ -5301,16 +5301,16 @@
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>401709</v>
+        <v>401710</v>
       </c>
       <c r="B246" t="str">
-        <v>POLLO GANSO EQUINO KG.</v>
+        <v>GANSO EQUINO KG.</v>
       </c>
       <c r="C246" t="str">
         <v/>
       </c>
       <c r="D246" t="str">
-        <v>1709</v>
+        <v>1710</v>
       </c>
       <c r="E246" t="str">
         <v>8290</v>
@@ -5321,19 +5321,19 @@
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>401710</v>
+        <v>401711</v>
       </c>
       <c r="B247" t="str">
-        <v>GANSO EQUINO KG.</v>
+        <v>PUNTA GANSO EQUINO KG.</v>
       </c>
       <c r="C247" t="str">
         <v/>
       </c>
       <c r="D247" t="str">
-        <v>1710</v>
+        <v>1711</v>
       </c>
       <c r="E247" t="str">
-        <v>8290</v>
+        <v>7990</v>
       </c>
       <c r="F247" t="str">
         <v>Por peso</v>
@@ -5341,19 +5341,19 @@
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>401711</v>
+        <v>401713</v>
       </c>
       <c r="B248" t="str">
-        <v>PUNTA GANSO EQUINO KG.</v>
+        <v>POSTA NEGRA EQUINO KG.</v>
       </c>
       <c r="C248" t="str">
         <v/>
       </c>
       <c r="D248" t="str">
-        <v>1711</v>
+        <v>1713</v>
       </c>
       <c r="E248" t="str">
-        <v>7990</v>
+        <v>9490</v>
       </c>
       <c r="F248" t="str">
         <v>Por peso</v>
@@ -5361,16 +5361,16 @@
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>401713</v>
+        <v>401714</v>
       </c>
       <c r="B249" t="str">
-        <v>POSTA NEGRA EQUINO KG.</v>
+        <v>POSTA ROSADA EQUINO KG</v>
       </c>
       <c r="C249" t="str">
         <v/>
       </c>
       <c r="D249" t="str">
-        <v>1713</v>
+        <v>1714</v>
       </c>
       <c r="E249" t="str">
         <v>9490</v>
@@ -5381,19 +5381,19 @@
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>401714</v>
+        <v>401715</v>
       </c>
       <c r="B250" t="str">
-        <v>POSTA ROSADA EQUINO KG</v>
+        <v>PALANCA EQUINO KG.</v>
       </c>
       <c r="C250" t="str">
         <v/>
       </c>
       <c r="D250" t="str">
-        <v>1714</v>
+        <v>1715</v>
       </c>
       <c r="E250" t="str">
-        <v>9490</v>
+        <v>8290</v>
       </c>
       <c r="F250" t="str">
         <v>Por peso</v>
@@ -5401,19 +5401,19 @@
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>401715</v>
+        <v>401716</v>
       </c>
       <c r="B251" t="str">
-        <v>PALANCA EQUINO KG.</v>
+        <v>ABASTERO EQUINO KG.</v>
       </c>
       <c r="C251" t="str">
         <v/>
       </c>
       <c r="D251" t="str">
-        <v>1715</v>
+        <v>1716</v>
       </c>
       <c r="E251" t="str">
-        <v>8290</v>
+        <v>7990</v>
       </c>
       <c r="F251" t="str">
         <v>Por peso</v>
@@ -5421,19 +5421,19 @@
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>401716</v>
+        <v>401717</v>
       </c>
       <c r="B252" t="str">
-        <v>ABASTERO EQUINO KG.</v>
+        <v>TAPABARRIGA EQUINO KG.</v>
       </c>
       <c r="C252" t="str">
         <v/>
       </c>
       <c r="D252" t="str">
-        <v>1716</v>
+        <v>1717</v>
       </c>
       <c r="E252" t="str">
-        <v>7990</v>
+        <v>6690</v>
       </c>
       <c r="F252" t="str">
         <v>Por peso</v>
@@ -5441,16 +5441,16 @@
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>401717</v>
+        <v>401718</v>
       </c>
       <c r="B253" t="str">
-        <v>TAPABARRIGA EQUINO KG.</v>
+        <v>POLLO BARRIGA EQUINO KG.</v>
       </c>
       <c r="C253" t="str">
         <v/>
       </c>
       <c r="D253" t="str">
-        <v>1717</v>
+        <v>1718</v>
       </c>
       <c r="E253" t="str">
         <v>6690</v>
@@ -5461,19 +5461,19 @@
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>401718</v>
+        <v>401719</v>
       </c>
       <c r="B254" t="str">
-        <v>POLLO BARRIGA EQUINO KG.</v>
+        <v>LOMO VETADO EQUINO KG.</v>
       </c>
       <c r="C254" t="str">
         <v/>
       </c>
       <c r="D254" t="str">
-        <v>1718</v>
+        <v>1719</v>
       </c>
       <c r="E254" t="str">
-        <v>6690</v>
+        <v>11490</v>
       </c>
       <c r="F254" t="str">
         <v>Por peso</v>
@@ -5481,19 +5481,19 @@
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>401719</v>
+        <v>401720</v>
       </c>
       <c r="B255" t="str">
-        <v>LOMO VETADO EQUINO KG.</v>
+        <v>POSTA PALETA EQUINO KG.</v>
       </c>
       <c r="C255" t="str">
         <v/>
       </c>
       <c r="D255" t="str">
-        <v>1719</v>
+        <v>1720</v>
       </c>
       <c r="E255" t="str">
-        <v>11490</v>
+        <v>9490</v>
       </c>
       <c r="F255" t="str">
         <v>Por peso</v>
@@ -5501,19 +5501,19 @@
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>401720</v>
+        <v>401721</v>
       </c>
       <c r="B256" t="str">
-        <v>POSTA PALETA EQUINO KG.</v>
+        <v>PUNTA PALETA EQUINO KG.</v>
       </c>
       <c r="C256" t="str">
         <v/>
       </c>
       <c r="D256" t="str">
-        <v>1720</v>
+        <v>1721</v>
       </c>
       <c r="E256" t="str">
-        <v>9490</v>
+        <v>7990</v>
       </c>
       <c r="F256" t="str">
         <v>Por peso</v>
@@ -5521,19 +5521,19 @@
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>401721</v>
+        <v>401722</v>
       </c>
       <c r="B257" t="str">
-        <v>PUNTA PALETA EQUINO KG.</v>
+        <v>CHOCLILLO EQUINO KG.</v>
       </c>
       <c r="C257" t="str">
         <v/>
       </c>
       <c r="D257" t="str">
-        <v>1721</v>
+        <v>1722</v>
       </c>
       <c r="E257" t="str">
-        <v>7990</v>
+        <v>8490</v>
       </c>
       <c r="F257" t="str">
         <v>Por peso</v>
@@ -5541,16 +5541,16 @@
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>401722</v>
+        <v>401723</v>
       </c>
       <c r="B258" t="str">
-        <v>CHOCLILLO EQUINO KG.</v>
+        <v>ASADO CARNICERO EQUINO KG.</v>
       </c>
       <c r="C258" t="str">
         <v/>
       </c>
       <c r="D258" t="str">
-        <v>1722</v>
+        <v>1723</v>
       </c>
       <c r="E258" t="str">
         <v>8490</v>
@@ -5561,16 +5561,16 @@
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>401723</v>
+        <v>401724</v>
       </c>
       <c r="B259" t="str">
-        <v>ASADO CARNICERO EQUINO KG.</v>
+        <v>PLATEADA EQUINO KG.</v>
       </c>
       <c r="C259" t="str">
         <v/>
       </c>
       <c r="D259" t="str">
-        <v>1723</v>
+        <v>1724</v>
       </c>
       <c r="E259" t="str">
         <v>8490</v>
@@ -5581,16 +5581,16 @@
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>401724</v>
+        <v>401725</v>
       </c>
       <c r="B260" t="str">
-        <v>PLATEADA EQUINO KG.</v>
+        <v>SOBRECOSTILLA EQUINO KG.</v>
       </c>
       <c r="C260" t="str">
         <v/>
       </c>
       <c r="D260" t="str">
-        <v>1724</v>
+        <v>1725</v>
       </c>
       <c r="E260" t="str">
         <v>8490</v>
@@ -5601,16 +5601,16 @@
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>401725</v>
+        <v>401726</v>
       </c>
       <c r="B261" t="str">
-        <v>SOBRECOSTILLA EQUINO KG.</v>
+        <v>HUACHALOMO EQUINO KG.</v>
       </c>
       <c r="C261" t="str">
         <v/>
       </c>
       <c r="D261" t="str">
-        <v>1725</v>
+        <v>1726</v>
       </c>
       <c r="E261" t="str">
         <v>8490</v>
@@ -5621,19 +5621,19 @@
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>401726</v>
+        <v>401727</v>
       </c>
       <c r="B262" t="str">
-        <v>HUACHALOMO EQUINO KG.</v>
+        <v>TAPAPECHO EQUINO KG.</v>
       </c>
       <c r="C262" t="str">
         <v/>
       </c>
       <c r="D262" t="str">
-        <v>1726</v>
+        <v>1727</v>
       </c>
       <c r="E262" t="str">
-        <v>8490</v>
+        <v>5690</v>
       </c>
       <c r="F262" t="str">
         <v>Por peso</v>
@@ -5641,19 +5641,19 @@
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>401727</v>
+        <v>401729</v>
       </c>
       <c r="B263" t="str">
-        <v>TAPAPECHO EQUINO KG.</v>
+        <v>ENTRANAS EQUINO KG.</v>
       </c>
       <c r="C263" t="str">
         <v/>
       </c>
       <c r="D263" t="str">
-        <v>1727</v>
+        <v>1729</v>
       </c>
       <c r="E263" t="str">
-        <v>5690</v>
+        <v>6490</v>
       </c>
       <c r="F263" t="str">
         <v>Por peso</v>
@@ -5661,19 +5661,19 @@
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>401729</v>
+        <v>401730</v>
       </c>
       <c r="B264" t="str">
-        <v>ENTRANAS EQUINO KG.</v>
+        <v>MALAYA EQUINO KG.</v>
       </c>
       <c r="C264" t="str">
         <v/>
       </c>
       <c r="D264" t="str">
-        <v>1729</v>
+        <v>1730</v>
       </c>
       <c r="E264" t="str">
-        <v>6490</v>
+        <v>2690</v>
       </c>
       <c r="F264" t="str">
         <v>Por peso</v>
@@ -5681,19 +5681,19 @@
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>401730</v>
+        <v>401731</v>
       </c>
       <c r="B265" t="str">
-        <v>MALAYA EQUINO KG.</v>
+        <v>CARNE MOLIDA CTE EQUINO KG.</v>
       </c>
       <c r="C265" t="str">
         <v/>
       </c>
       <c r="D265" t="str">
-        <v>1730</v>
+        <v>1731</v>
       </c>
       <c r="E265" t="str">
-        <v>2690</v>
+        <v>7290</v>
       </c>
       <c r="F265" t="str">
         <v>Por peso</v>
@@ -5701,19 +5701,19 @@
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>401731</v>
+        <v>401732</v>
       </c>
       <c r="B266" t="str">
-        <v>CARNE MOLIDA CTE EQUINO KG.</v>
+        <v>CARNE MOLIDA ESPEC. EQUINO KG.</v>
       </c>
       <c r="C266" t="str">
         <v/>
       </c>
       <c r="D266" t="str">
-        <v>1731</v>
+        <v>1732</v>
       </c>
       <c r="E266" t="str">
-        <v>7290</v>
+        <v>8290</v>
       </c>
       <c r="F266" t="str">
         <v>Por peso</v>
@@ -5721,19 +5721,19 @@
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>401732</v>
+        <v>401733</v>
       </c>
       <c r="B267" t="str">
-        <v>CARNE MOLIDA ESPEC. EQUINO KG.</v>
+        <v>ASADO DE TIRA EQUINO KG.</v>
       </c>
       <c r="C267" t="str">
         <v/>
       </c>
       <c r="D267" t="str">
-        <v>1732</v>
+        <v>1733</v>
       </c>
       <c r="E267" t="str">
-        <v>8290</v>
+        <v>3990</v>
       </c>
       <c r="F267" t="str">
         <v>Por peso</v>
@@ -5741,19 +5741,19 @@
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>401733</v>
+        <v>401734</v>
       </c>
       <c r="B268" t="str">
-        <v>ASADO DE TIRA EQUINO KG.</v>
+        <v>OSOBUCO MANO PIERNA EQUINO KG.</v>
       </c>
       <c r="C268" t="str">
         <v/>
       </c>
       <c r="D268" t="str">
-        <v>1733</v>
+        <v>1734</v>
       </c>
       <c r="E268" t="str">
-        <v>3990</v>
+        <v>2990</v>
       </c>
       <c r="F268" t="str">
         <v>Por peso</v>
@@ -5761,16 +5761,16 @@
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>401734</v>
+        <v>401735</v>
       </c>
       <c r="B269" t="str">
-        <v>OSOBUCO MANO PIERNA EQUINO KG.</v>
+        <v>LAGARTO MANO EQUINO KG.</v>
       </c>
       <c r="C269" t="str">
         <v/>
       </c>
       <c r="D269" t="str">
-        <v>1734</v>
+        <v>1735</v>
       </c>
       <c r="E269" t="str">
         <v>2990</v>
@@ -5781,19 +5781,19 @@
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>401735</v>
+        <v>401736</v>
       </c>
       <c r="B270" t="str">
-        <v>LAGARTO MANO EQUINO KG.</v>
+        <v>ALETILLA EQUINO KG.</v>
       </c>
       <c r="C270" t="str">
         <v/>
       </c>
       <c r="D270" t="str">
-        <v>1735</v>
+        <v>1736</v>
       </c>
       <c r="E270" t="str">
-        <v>2990</v>
+        <v>1990</v>
       </c>
       <c r="F270" t="str">
         <v>Por peso</v>
@@ -5801,16 +5801,16 @@
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>401736</v>
+        <v>401737</v>
       </c>
       <c r="B271" t="str">
-        <v>ALETILLA EQUINO KG.</v>
+        <v>COLUDA EQUINO KG.</v>
       </c>
       <c r="C271" t="str">
         <v/>
       </c>
       <c r="D271" t="str">
-        <v>1736</v>
+        <v>1737</v>
       </c>
       <c r="E271" t="str">
         <v>1990</v>
@@ -5821,19 +5821,19 @@
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>401737</v>
+        <v>401738</v>
       </c>
       <c r="B272" t="str">
-        <v>COLUDA EQUINO KG.</v>
+        <v>HUESO CARNUDO EQUINO KG.</v>
       </c>
       <c r="C272" t="str">
         <v/>
       </c>
       <c r="D272" t="str">
-        <v>1737</v>
+        <v>1738</v>
       </c>
       <c r="E272" t="str">
-        <v>1990</v>
+        <v>1790</v>
       </c>
       <c r="F272" t="str">
         <v>Por peso</v>
@@ -5841,19 +5841,19 @@
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>401738</v>
+        <v>401739</v>
       </c>
       <c r="B273" t="str">
-        <v>HUESO CARNUDO EQUINO KG.</v>
+        <v>HUESO PELADO EQUINO KG.</v>
       </c>
       <c r="C273" t="str">
         <v/>
       </c>
       <c r="D273" t="str">
-        <v>1738</v>
+        <v>1739</v>
       </c>
       <c r="E273" t="str">
-        <v>1790</v>
+        <v>890</v>
       </c>
       <c r="F273" t="str">
         <v>Por peso</v>
@@ -5861,19 +5861,19 @@
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>401739</v>
+        <v>401740</v>
       </c>
       <c r="B274" t="str">
-        <v>HUESO PELADO EQUINO KG.</v>
+        <v>COLA EQUINO KG.</v>
       </c>
       <c r="C274" t="str">
         <v/>
       </c>
       <c r="D274" t="str">
-        <v>1739</v>
+        <v>1740</v>
       </c>
       <c r="E274" t="str">
-        <v>890</v>
+        <v>790</v>
       </c>
       <c r="F274" t="str">
         <v>Por peso</v>
@@ -5881,19 +5881,19 @@
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>401740</v>
+        <v>401741</v>
       </c>
       <c r="B275" t="str">
-        <v>COLA EQUINO KG.</v>
+        <v>GRASA EQUINO KG.</v>
       </c>
       <c r="C275" t="str">
         <v/>
       </c>
       <c r="D275" t="str">
-        <v>1740</v>
+        <v>1741</v>
       </c>
       <c r="E275" t="str">
-        <v>790</v>
+        <v>690</v>
       </c>
       <c r="F275" t="str">
         <v>Por peso</v>
@@ -5901,19 +5901,19 @@
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>401741</v>
+        <v>401535</v>
       </c>
       <c r="B276" t="str">
-        <v>GRASA EQUINO KG.</v>
+        <v>TRUTRO CUARTO USA KILO</v>
       </c>
       <c r="C276" t="str">
         <v/>
       </c>
       <c r="D276" t="str">
-        <v>1741</v>
+        <v>1535</v>
       </c>
       <c r="E276" t="str">
-        <v>690</v>
+        <v>2390</v>
       </c>
       <c r="F276" t="str">
         <v>Por peso</v>
@@ -5921,19 +5921,19 @@
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>401535</v>
+        <v>401751</v>
       </c>
       <c r="B277" t="str">
-        <v>TRUTRO CUARTO USA KILO</v>
+        <v>GUATA EQUINO KG</v>
       </c>
       <c r="C277" t="str">
         <v/>
       </c>
       <c r="D277" t="str">
-        <v>1535</v>
+        <v>1751</v>
       </c>
       <c r="E277" t="str">
-        <v>2390</v>
+        <v>990</v>
       </c>
       <c r="F277" t="str">
         <v>Por peso</v>
@@ -5941,19 +5941,19 @@
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>401751</v>
+        <v>401752</v>
       </c>
       <c r="B278" t="str">
-        <v>GUATA EQUINO KG</v>
+        <v>HIGADO EQUINO</v>
       </c>
       <c r="C278" t="str">
         <v/>
       </c>
       <c r="D278" t="str">
-        <v>1751</v>
+        <v>1752</v>
       </c>
       <c r="E278" t="str">
-        <v>990</v>
+        <v>2490</v>
       </c>
       <c r="F278" t="str">
         <v>Por peso</v>
@@ -5961,19 +5961,19 @@
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>401752</v>
+        <v>401753</v>
       </c>
       <c r="B279" t="str">
-        <v>HIGADO EQUINO</v>
+        <v>CORAZON EQUINO</v>
       </c>
       <c r="C279" t="str">
         <v/>
       </c>
       <c r="D279" t="str">
-        <v>1752</v>
+        <v>1753</v>
       </c>
       <c r="E279" t="str">
-        <v>2490</v>
+        <v>990</v>
       </c>
       <c r="F279" t="str">
         <v>Por peso</v>
@@ -5981,19 +5981,19 @@
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>401753</v>
+        <v>401754</v>
       </c>
       <c r="B280" t="str">
-        <v>CORAZON EQUINO</v>
+        <v>LENGUA EQUINO</v>
       </c>
       <c r="C280" t="str">
         <v/>
       </c>
       <c r="D280" t="str">
-        <v>1753</v>
+        <v>1754</v>
       </c>
       <c r="E280" t="str">
-        <v>990</v>
+        <v>1990</v>
       </c>
       <c r="F280" t="str">
         <v>Por peso</v>
@@ -6001,19 +6001,19 @@
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>401754</v>
+        <v>401755</v>
       </c>
       <c r="B281" t="str">
-        <v>LENGUA EQUINO</v>
+        <v>CHUNCHULE EQUINO</v>
       </c>
       <c r="C281" t="str">
         <v/>
       </c>
       <c r="D281" t="str">
-        <v>1754</v>
+        <v>1755</v>
       </c>
       <c r="E281" t="str">
-        <v>1990</v>
+        <v>1490</v>
       </c>
       <c r="F281" t="str">
         <v>Por peso</v>
@@ -6021,19 +6021,19 @@
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>401755</v>
+        <v>401756</v>
       </c>
       <c r="B282" t="str">
-        <v>CHUNCHULE EQUINO</v>
+        <v>CHARCHAS EQUINO</v>
       </c>
       <c r="C282" t="str">
         <v/>
       </c>
       <c r="D282" t="str">
-        <v>1755</v>
+        <v>1756</v>
       </c>
       <c r="E282" t="str">
-        <v>1490</v>
+        <v>1190</v>
       </c>
       <c r="F282" t="str">
         <v>Por peso</v>
@@ -6041,19 +6041,19 @@
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>401756</v>
+        <v>401757</v>
       </c>
       <c r="B283" t="str">
-        <v>CHARCHAS EQUINO</v>
+        <v>RINONES EQUINO</v>
       </c>
       <c r="C283" t="str">
         <v/>
       </c>
       <c r="D283" t="str">
-        <v>1756</v>
+        <v>1757</v>
       </c>
       <c r="E283" t="str">
-        <v>1190</v>
+        <v>990</v>
       </c>
       <c r="F283" t="str">
         <v>Por peso</v>
@@ -6061,19 +6061,19 @@
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>401757</v>
+        <v>401696</v>
       </c>
       <c r="B284" t="str">
-        <v>RINONES EQUINO</v>
+        <v>V.POSTA PALETA BRA PORC.</v>
       </c>
       <c r="C284" t="str">
         <v/>
       </c>
       <c r="D284" t="str">
-        <v>1757</v>
+        <v>1696</v>
       </c>
       <c r="E284" t="str">
-        <v>990</v>
+        <v>9690</v>
       </c>
       <c r="F284" t="str">
         <v>Por peso</v>
@@ -6081,19 +6081,19 @@
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>401696</v>
+        <v>401094</v>
       </c>
       <c r="B285" t="str">
-        <v>V.POSTA PALETA BRA PORC.</v>
+        <v>V.SOBREC-HUACHA</v>
       </c>
       <c r="C285" t="str">
         <v/>
       </c>
       <c r="D285" t="str">
-        <v>1696</v>
+        <v>1094</v>
       </c>
       <c r="E285" t="str">
-        <v>9690</v>
+        <v>13490</v>
       </c>
       <c r="F285" t="str">
         <v>Por peso</v>
@@ -6101,19 +6101,19 @@
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>405865</v>
+        <v>402589</v>
       </c>
       <c r="B286" t="str">
-        <v>U.COGOTE NACIONAL</v>
+        <v>TRUTRO ENTERO CONG.AGROSUPER</v>
       </c>
       <c r="C286" t="str">
         <v/>
       </c>
       <c r="D286" t="str">
-        <v>5865</v>
+        <v>2589</v>
       </c>
       <c r="E286" t="str">
-        <v>12000</v>
+        <v>4990</v>
       </c>
       <c r="F286" t="str">
         <v>Por peso</v>
@@ -6121,19 +6121,19 @@
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>401094</v>
+        <v>402580</v>
       </c>
       <c r="B287" t="str">
-        <v>V.SOBREC-HUACHA</v>
+        <v>CHULETA VETADA IMP C</v>
       </c>
       <c r="C287" t="str">
         <v/>
       </c>
       <c r="D287" t="str">
-        <v>1094</v>
+        <v>2580</v>
       </c>
       <c r="E287" t="str">
-        <v>13490</v>
+        <v>5290</v>
       </c>
       <c r="F287" t="str">
         <v>Por peso</v>
@@ -6141,19 +6141,19 @@
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>402589</v>
+        <v>401396</v>
       </c>
       <c r="B288" t="str">
-        <v>TRUTRO ENTERO CONG.AGROSUPER</v>
+        <v>C.LAGARTO MANO</v>
       </c>
       <c r="C288" t="str">
         <v/>
       </c>
       <c r="D288" t="str">
-        <v>2589</v>
+        <v>1396</v>
       </c>
       <c r="E288" t="str">
-        <v>4990</v>
+        <v>9690</v>
       </c>
       <c r="F288" t="str">
         <v>Por peso</v>
@@ -6161,19 +6161,19 @@
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>402580</v>
+        <v>401390</v>
       </c>
       <c r="B289" t="str">
-        <v>CHULETA VETADA IMP C</v>
+        <v>C.PUNTA PALETA</v>
       </c>
       <c r="C289" t="str">
         <v/>
       </c>
       <c r="D289" t="str">
-        <v>2580</v>
+        <v>1390</v>
       </c>
       <c r="E289" t="str">
-        <v>5290</v>
+        <v>11990</v>
       </c>
       <c r="F289" t="str">
         <v>Por peso</v>
@@ -6181,19 +6181,19 @@
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>401396</v>
+        <v>402565</v>
       </c>
       <c r="B290" t="str">
-        <v>C.LAGARTO MANO</v>
+        <v>VACUNO DESPOSTADO V</v>
       </c>
       <c r="C290" t="str">
         <v/>
       </c>
       <c r="D290" t="str">
-        <v>1396</v>
+        <v>2565</v>
       </c>
       <c r="E290" t="str">
-        <v>9690</v>
+        <v>4500</v>
       </c>
       <c r="F290" t="str">
         <v>Por peso</v>
@@ -6201,19 +6201,19 @@
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>401390</v>
+        <v>402940</v>
       </c>
       <c r="B291" t="str">
-        <v>C.PUNTA PALETA</v>
+        <v>TRUTRO PARRILERO PAVO ARIZTIA</v>
       </c>
       <c r="C291" t="str">
         <v/>
       </c>
       <c r="D291" t="str">
-        <v>1390</v>
+        <v>2940</v>
       </c>
       <c r="E291" t="str">
-        <v>11990</v>
+        <v>10490</v>
       </c>
       <c r="F291" t="str">
         <v>Por peso</v>
@@ -6221,19 +6221,19 @@
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>402565</v>
+        <v>402858</v>
       </c>
       <c r="B292" t="str">
-        <v>VACUNO DESPOSTADO V</v>
+        <v>C.SOBRECOST HUACHALOMO CORTE AMERICANO</v>
       </c>
       <c r="C292" t="str">
         <v/>
       </c>
       <c r="D292" t="str">
-        <v>2565</v>
+        <v>2858</v>
       </c>
       <c r="E292" t="str">
-        <v>4500</v>
+        <v>12990</v>
       </c>
       <c r="F292" t="str">
         <v>Por peso</v>
@@ -6241,99 +6241,99 @@
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>402940</v>
+        <v>403559</v>
       </c>
       <c r="B293" t="str">
-        <v>TRUTRO PARRILERO PAVO ARIZTIA</v>
+        <v>TRUTRO CUARTO BRASIL CAJA 10 KG</v>
       </c>
       <c r="C293" t="str">
         <v/>
       </c>
       <c r="D293" t="str">
-        <v>2940</v>
+        <v>3559</v>
       </c>
       <c r="E293" t="str">
-        <v>10490</v>
+        <v>23990</v>
       </c>
       <c r="F293" t="str">
-        <v>Por peso</v>
+        <v>Por cantidad</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>402858</v>
+        <v>403566</v>
       </c>
       <c r="B294" t="str">
-        <v>C.SOBRECOST HUACHALOMO CORTE AMERICANO</v>
+        <v>TRUTRO CUARTO BLOCK CAJA 15</v>
       </c>
       <c r="C294" t="str">
         <v/>
       </c>
       <c r="D294" t="str">
-        <v>2858</v>
+        <v>3566</v>
       </c>
       <c r="E294" t="str">
-        <v>12990</v>
+        <v>37990</v>
       </c>
       <c r="F294" t="str">
-        <v>Por peso</v>
+        <v>Por cantidad</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>403559</v>
+        <v>405099</v>
       </c>
       <c r="B295" t="str">
-        <v>TRUTRO CUARTO BRASIL CAJA 10 KG</v>
+        <v>CORAZON CONG DESGRASADO</v>
       </c>
       <c r="C295" t="str">
         <v/>
       </c>
       <c r="D295" t="str">
-        <v>3559</v>
+        <v>5099</v>
       </c>
       <c r="E295" t="str">
-        <v>23990</v>
+        <v>4990</v>
       </c>
       <c r="F295" t="str">
-        <v>Por cantidad</v>
+        <v>Por peso</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>403566</v>
+        <v>409778</v>
       </c>
       <c r="B296" t="str">
-        <v>TRUTRO CUARTO BLOCK CAJA 15</v>
+        <v>CHULETA CENTRO SUPERCERDO</v>
       </c>
       <c r="C296" t="str">
         <v/>
       </c>
       <c r="D296" t="str">
-        <v>3566</v>
+        <v>9778</v>
       </c>
       <c r="E296" t="str">
-        <v>37990</v>
+        <v>6490</v>
       </c>
       <c r="F296" t="str">
-        <v>Por cantidad</v>
+        <v>Por peso</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>405099</v>
+        <v>405662</v>
       </c>
       <c r="B297" t="str">
-        <v>CORAZON CONG DESGRASADO</v>
+        <v>ENTRECOT EQUINO VARA</v>
       </c>
       <c r="C297" t="str">
         <v/>
       </c>
       <c r="D297" t="str">
-        <v>5099</v>
+        <v>5662</v>
       </c>
       <c r="E297" t="str">
-        <v>4990</v>
+        <v>9990</v>
       </c>
       <c r="F297" t="str">
         <v>Por peso</v>
@@ -6341,19 +6341,19 @@
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>409778</v>
+        <v>408079</v>
       </c>
       <c r="B298" t="str">
-        <v>CHULETA CENTRO SUPERCERDO</v>
+        <v>HIGADO IMP CONG</v>
       </c>
       <c r="C298" t="str">
         <v/>
       </c>
       <c r="D298" t="str">
-        <v>9778</v>
+        <v>8079</v>
       </c>
       <c r="E298" t="str">
-        <v>6490</v>
+        <v>4990</v>
       </c>
       <c r="F298" t="str">
         <v>Por peso</v>
@@ -6361,19 +6361,19 @@
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>405662</v>
+        <v>408081</v>
       </c>
       <c r="B299" t="str">
-        <v>ENTRECOT EQUINO VARA</v>
+        <v>HUESO COGOTE TIPO V PROCARNE</v>
       </c>
       <c r="C299" t="str">
         <v/>
       </c>
       <c r="D299" t="str">
-        <v>5662</v>
+        <v>8081</v>
       </c>
       <c r="E299" t="str">
-        <v>9990</v>
+        <v>6990</v>
       </c>
       <c r="F299" t="str">
         <v>Por peso</v>
@@ -6381,16 +6381,16 @@
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>408079</v>
+        <v>409782</v>
       </c>
       <c r="B300" t="str">
-        <v>HIGADO IMP CONG</v>
+        <v>GUATA SEGUNDA PROCAR</v>
       </c>
       <c r="C300" t="str">
         <v/>
       </c>
       <c r="D300" t="str">
-        <v>8079</v>
+        <v>9782</v>
       </c>
       <c r="E300" t="str">
         <v>4990</v>
@@ -6401,19 +6401,19 @@
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>408081</v>
+        <v>409783</v>
       </c>
       <c r="B301" t="str">
-        <v>HUESO COGOTE TIPO V PROCARNE</v>
+        <v>COLA DE VACUNO PROCARNE</v>
       </c>
       <c r="C301" t="str">
         <v/>
       </c>
       <c r="D301" t="str">
-        <v>8081</v>
+        <v>9783</v>
       </c>
       <c r="E301" t="str">
-        <v>6990</v>
+        <v>3990</v>
       </c>
       <c r="F301" t="str">
         <v>Por peso</v>
@@ -6421,19 +6421,19 @@
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>409782</v>
+        <v>409791</v>
       </c>
       <c r="B302" t="str">
-        <v>GUATA SEGUNDA PROCAR</v>
+        <v>HIGADO PROCARNE</v>
       </c>
       <c r="C302" t="str">
         <v/>
       </c>
       <c r="D302" t="str">
-        <v>9782</v>
+        <v>9791</v>
       </c>
       <c r="E302" t="str">
-        <v>4990</v>
+        <v>4290</v>
       </c>
       <c r="F302" t="str">
         <v>Por peso</v>
@@ -6441,19 +6441,19 @@
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>409783</v>
+        <v>405878</v>
       </c>
       <c r="B303" t="str">
-        <v>COLA DE VACUNO PROCARNE</v>
+        <v>V.ENTRANA VACUNO IMP PARAGUAY</v>
       </c>
       <c r="C303" t="str">
         <v/>
       </c>
       <c r="D303" t="str">
-        <v>9783</v>
+        <v>5878</v>
       </c>
       <c r="E303" t="str">
-        <v>3990</v>
+        <v>18990</v>
       </c>
       <c r="F303" t="str">
         <v>Por peso</v>
@@ -6461,19 +6461,19 @@
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>409791</v>
+        <v>405879</v>
       </c>
       <c r="B304" t="str">
-        <v>HIGADO PROCARNE</v>
+        <v>PATAS DE POLLO CONG ARIZTIA</v>
       </c>
       <c r="C304" t="str">
         <v/>
       </c>
       <c r="D304" t="str">
-        <v>9791</v>
+        <v>5879</v>
       </c>
       <c r="E304" t="str">
-        <v>4290</v>
+        <v>2990</v>
       </c>
       <c r="F304" t="str">
         <v>Por peso</v>
@@ -6481,19 +6481,19 @@
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>405878</v>
+        <v>409100</v>
       </c>
       <c r="B305" t="str">
-        <v>V.ENTRANA VACUNO IMP PARAGUAY</v>
+        <v>C.MANTA TRASERA CONG</v>
       </c>
       <c r="C305" t="str">
         <v/>
       </c>
       <c r="D305" t="str">
-        <v>5878</v>
+        <v>9100</v>
       </c>
       <c r="E305" t="str">
-        <v>18990</v>
+        <v>7290</v>
       </c>
       <c r="F305" t="str">
         <v>Por peso</v>
@@ -6501,19 +6501,19 @@
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>405879</v>
+        <v>405893</v>
       </c>
       <c r="B306" t="str">
-        <v>PATAS DE POLLO CONG ARIZTIA</v>
+        <v>COGOTE EQUINO VARA</v>
       </c>
       <c r="C306" t="str">
         <v/>
       </c>
       <c r="D306" t="str">
-        <v>5879</v>
+        <v>5893</v>
       </c>
       <c r="E306" t="str">
-        <v>2990</v>
+        <v>2490</v>
       </c>
       <c r="F306" t="str">
         <v>Por peso</v>
@@ -6521,19 +6521,19 @@
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>409100</v>
+        <v>403456</v>
       </c>
       <c r="B307" t="str">
-        <v>C.MANTA TRASERA CONG</v>
+        <v>TRUTRO CUARTO AGROSUPER</v>
       </c>
       <c r="C307" t="str">
         <v/>
       </c>
       <c r="D307" t="str">
-        <v>9100</v>
+        <v>3456</v>
       </c>
       <c r="E307" t="str">
-        <v>7290</v>
+        <v>5690</v>
       </c>
       <c r="F307" t="str">
         <v>Por peso</v>
@@ -6541,19 +6541,19 @@
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>405893</v>
+        <v>402130</v>
       </c>
       <c r="B308" t="str">
-        <v>COGOTE EQUINO VARA</v>
+        <v>V.COSTILLA ARQUEADA</v>
       </c>
       <c r="C308" t="str">
         <v/>
       </c>
       <c r="D308" t="str">
-        <v>5893</v>
+        <v>2130</v>
       </c>
       <c r="E308" t="str">
-        <v>2490</v>
+        <v>4990</v>
       </c>
       <c r="F308" t="str">
         <v>Por peso</v>
@@ -6561,19 +6561,19 @@
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>403456</v>
+        <v>404021</v>
       </c>
       <c r="B309" t="str">
-        <v>TRUTRO CUARTO AGROSUPER</v>
+        <v>C.COSTILLA ARQUEADA</v>
       </c>
       <c r="C309" t="str">
         <v/>
       </c>
       <c r="D309" t="str">
-        <v>3456</v>
+        <v>4021</v>
       </c>
       <c r="E309" t="str">
-        <v>5690</v>
+        <v>4990</v>
       </c>
       <c r="F309" t="str">
         <v>Por peso</v>
@@ -6581,19 +6581,19 @@
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>402130</v>
+        <v>404789</v>
       </c>
       <c r="B310" t="str">
-        <v>V.COSTILLA ARQUEADA</v>
+        <v>COSTILLAR AHUMADO DON RODRIGO</v>
       </c>
       <c r="C310" t="str">
         <v/>
       </c>
       <c r="D310" t="str">
-        <v>2130</v>
+        <v>4789</v>
       </c>
       <c r="E310" t="str">
-        <v>4990</v>
+        <v>8990</v>
       </c>
       <c r="F310" t="str">
         <v>Por peso</v>
@@ -6601,19 +6601,19 @@
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>404021</v>
+        <v>404880</v>
       </c>
       <c r="B311" t="str">
-        <v>C.COSTILLA ARQUEADA</v>
+        <v>COSTILLAR ALINADO DON RODRIGO</v>
       </c>
       <c r="C311" t="str">
         <v/>
       </c>
       <c r="D311" t="str">
-        <v>4021</v>
+        <v>4880</v>
       </c>
       <c r="E311" t="str">
-        <v>4990</v>
+        <v>8990</v>
       </c>
       <c r="F311" t="str">
         <v>Por peso</v>
@@ -6621,16 +6621,16 @@
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>404789</v>
+        <v>402352</v>
       </c>
       <c r="B312" t="str">
-        <v>COSTILLAR AHUMADO DON RODRIGO</v>
+        <v>COSTILLAR BARBECUE DON RODRIGO</v>
       </c>
       <c r="C312" t="str">
         <v/>
       </c>
       <c r="D312" t="str">
-        <v>4789</v>
+        <v>2352</v>
       </c>
       <c r="E312" t="str">
         <v>8990</v>
@@ -6641,19 +6641,19 @@
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>404880</v>
+        <v>408780</v>
       </c>
       <c r="B313" t="str">
-        <v>COSTILLAR ALINADO DON RODRIGO</v>
+        <v>COSTILLAR CRIOLLO COOK AND FUN</v>
       </c>
       <c r="C313" t="str">
         <v/>
       </c>
       <c r="D313" t="str">
-        <v>4880</v>
+        <v>8780</v>
       </c>
       <c r="E313" t="str">
-        <v>8990</v>
+        <v>8490</v>
       </c>
       <c r="F313" t="str">
         <v>Por peso</v>
@@ -6661,19 +6661,19 @@
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>402352</v>
+        <v>408781</v>
       </c>
       <c r="B314" t="str">
-        <v>COSTILLAR BARBECUE DON RODRIGO</v>
+        <v>COSTILLAR NATURAL COOK-FUN</v>
       </c>
       <c r="C314" t="str">
         <v/>
       </c>
       <c r="D314" t="str">
-        <v>2352</v>
+        <v>8781</v>
       </c>
       <c r="E314" t="str">
-        <v>8990</v>
+        <v>8490</v>
       </c>
       <c r="F314" t="str">
         <v>Por peso</v>
@@ -6681,19 +6681,19 @@
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>408780</v>
+        <v>403231</v>
       </c>
       <c r="B315" t="str">
-        <v>COSTILLAR CRIOLLO COOK AND FUN</v>
+        <v>ALA PUCHERO SUPERPOLLO KG</v>
       </c>
       <c r="C315" t="str">
         <v/>
       </c>
       <c r="D315" t="str">
-        <v>8780</v>
+        <v>3231</v>
       </c>
       <c r="E315" t="str">
-        <v>8490</v>
+        <v>3490</v>
       </c>
       <c r="F315" t="str">
         <v>Por peso</v>
@@ -6701,19 +6701,19 @@
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>408781</v>
+        <v>400610</v>
       </c>
       <c r="B316" t="str">
-        <v>COSTILLAR NATURAL COOK-FUN</v>
+        <v>TRUTRO CORTO POLLO BAND. H-50 SUPER</v>
       </c>
       <c r="C316" t="str">
         <v/>
       </c>
       <c r="D316" t="str">
-        <v>8781</v>
+        <v>0610</v>
       </c>
       <c r="E316" t="str">
-        <v>8490</v>
+        <v>5490</v>
       </c>
       <c r="F316" t="str">
         <v>Por peso</v>
@@ -6721,19 +6721,19 @@
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>403231</v>
+        <v>401355</v>
       </c>
       <c r="B317" t="str">
-        <v>ALA PUCHERO SUPERPOLLO KG</v>
+        <v>V.ASIENTO BRASIL VACIO IMP ENTERO</v>
       </c>
       <c r="C317" t="str">
         <v/>
       </c>
       <c r="D317" t="str">
-        <v>3231</v>
+        <v>1355</v>
       </c>
       <c r="E317" t="str">
-        <v>3490</v>
+        <v>12990</v>
       </c>
       <c r="F317" t="str">
         <v>Por peso</v>
@@ -6741,19 +6741,19 @@
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>400610</v>
+        <v>408180</v>
       </c>
       <c r="B318" t="str">
-        <v>TRUTRO CORTO POLLO BAND. H-50 SUPER</v>
+        <v>PECHUGA BANDEJA ENTERA KG SUPERPOLLO</v>
       </c>
       <c r="C318" t="str">
         <v/>
       </c>
       <c r="D318" t="str">
-        <v>0610</v>
+        <v>8180</v>
       </c>
       <c r="E318" t="str">
-        <v>5490</v>
+        <v>6990</v>
       </c>
       <c r="F318" t="str">
         <v>Por peso</v>
@@ -6761,19 +6761,19 @@
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>401355</v>
+        <v>403201</v>
       </c>
       <c r="B319" t="str">
-        <v>V.ASIENTO BRASIL VACIO IMP ENTERO</v>
+        <v>COGOTE PAVO CONG ARIZTIA</v>
       </c>
       <c r="C319" t="str">
         <v/>
       </c>
       <c r="D319" t="str">
-        <v>1355</v>
+        <v>3201</v>
       </c>
       <c r="E319" t="str">
-        <v>12990</v>
+        <v>5490</v>
       </c>
       <c r="F319" t="str">
         <v>Por peso</v>
@@ -6781,19 +6781,19 @@
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>408180</v>
+        <v>406678</v>
       </c>
       <c r="B320" t="str">
-        <v>PECHUGA BANDEJA ENTERA KG SUPERPOLLO</v>
+        <v>PATAS POLLO IQF GRANEL SUPERPOLLO</v>
       </c>
       <c r="C320" t="str">
         <v/>
       </c>
       <c r="D320" t="str">
-        <v>8180</v>
+        <v>6678</v>
       </c>
       <c r="E320" t="str">
-        <v>6990</v>
+        <v>1690</v>
       </c>
       <c r="F320" t="str">
         <v>Por peso</v>
@@ -6801,19 +6801,19 @@
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>403201</v>
+        <v>403032</v>
       </c>
       <c r="B321" t="str">
-        <v>COGOTE PAVO CONG ARIZTIA</v>
+        <v>PULPA PIERNA 57 SUPERCERDO</v>
       </c>
       <c r="C321" t="str">
         <v/>
       </c>
       <c r="D321" t="str">
-        <v>3201</v>
+        <v>3032</v>
       </c>
       <c r="E321" t="str">
-        <v>5490</v>
+        <v>8290</v>
       </c>
       <c r="F321" t="str">
         <v>Por peso</v>
@@ -6821,19 +6821,19 @@
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>406678</v>
+        <v>407002</v>
       </c>
       <c r="B322" t="str">
-        <v>PATAS POLLO IQF GRANEL SUPERPOLLO</v>
+        <v>COSTILLAR 75 SUPERCERDO</v>
       </c>
       <c r="C322" t="str">
         <v/>
       </c>
       <c r="D322" t="str">
-        <v>6678</v>
+        <v>7002</v>
       </c>
       <c r="E322" t="str">
-        <v>1690</v>
+        <v>10990</v>
       </c>
       <c r="F322" t="str">
         <v>Por peso</v>
@@ -6841,19 +6841,19 @@
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>403032</v>
+        <v>407983</v>
       </c>
       <c r="B323" t="str">
-        <v>PULPA PIERNA 57 SUPERCERDO</v>
+        <v>PANA POLLO DON POLLO</v>
       </c>
       <c r="C323" t="str">
         <v/>
       </c>
       <c r="D323" t="str">
-        <v>3032</v>
+        <v>7983</v>
       </c>
       <c r="E323" t="str">
-        <v>8290</v>
+        <v>2990</v>
       </c>
       <c r="F323" t="str">
         <v>Por peso</v>
@@ -6861,19 +6861,19 @@
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>407002</v>
+        <v>407981</v>
       </c>
       <c r="B324" t="str">
-        <v>COSTILLAR 75 SUPERCERDO</v>
+        <v>GARRAS O PATAS POLLO DON POLLO</v>
       </c>
       <c r="C324" t="str">
         <v/>
       </c>
       <c r="D324" t="str">
-        <v>7002</v>
+        <v>7981</v>
       </c>
       <c r="E324" t="str">
-        <v>10990</v>
+        <v>1490</v>
       </c>
       <c r="F324" t="str">
         <v>Por peso</v>
@@ -6881,19 +6881,19 @@
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>407983</v>
+        <v>407980</v>
       </c>
       <c r="B325" t="str">
-        <v>PANA POLLO DON POLLO</v>
+        <v>CONTRE POLLO DON POLLO</v>
       </c>
       <c r="C325" t="str">
         <v/>
       </c>
       <c r="D325" t="str">
-        <v>7983</v>
+        <v>7980</v>
       </c>
       <c r="E325" t="str">
-        <v>2990</v>
+        <v>3690</v>
       </c>
       <c r="F325" t="str">
         <v>Por peso</v>
@@ -6901,19 +6901,19 @@
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>407981</v>
+        <v>402450</v>
       </c>
       <c r="B326" t="str">
-        <v>GARRAS O PATAS POLLO DON POLLO</v>
+        <v>COGOTE POLLO DON POLLO</v>
       </c>
       <c r="C326" t="str">
         <v/>
       </c>
       <c r="D326" t="str">
-        <v>7981</v>
+        <v>2450</v>
       </c>
       <c r="E326" t="str">
-        <v>1490</v>
+        <v>1290</v>
       </c>
       <c r="F326" t="str">
         <v>Por peso</v>
@@ -6921,19 +6921,19 @@
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>407980</v>
+        <v>404041</v>
       </c>
       <c r="B327" t="str">
-        <v>CONTRE POLLO DON POLLO</v>
+        <v>COSTILLAR TRADICIONAL SUPERCERDO.</v>
       </c>
       <c r="C327" t="str">
         <v/>
       </c>
       <c r="D327" t="str">
-        <v>7980</v>
+        <v>4041</v>
       </c>
       <c r="E327" t="str">
-        <v>3690</v>
+        <v>12690</v>
       </c>
       <c r="F327" t="str">
         <v>Por peso</v>
@@ -6941,19 +6941,19 @@
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>402450</v>
+        <v>408850</v>
       </c>
       <c r="B328" t="str">
-        <v>COGOTE POLLO DON POLLO</v>
+        <v>BABY BACK RIBS AMERICANO SUPERCERDO</v>
       </c>
       <c r="C328" t="str">
         <v/>
       </c>
       <c r="D328" t="str">
-        <v>2450</v>
+        <v>8850</v>
       </c>
       <c r="E328" t="str">
-        <v>1290</v>
+        <v>14290</v>
       </c>
       <c r="F328" t="str">
         <v>Por peso</v>
@@ -6961,19 +6961,19 @@
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>404041</v>
+        <v>409777</v>
       </c>
       <c r="B329" t="str">
-        <v>COSTILLAR TRADICIONAL SUPERCERDO.</v>
+        <v>CHULETA VETADA SUPERCERDO</v>
       </c>
       <c r="C329" t="str">
         <v/>
       </c>
       <c r="D329" t="str">
-        <v>4041</v>
+        <v>9777</v>
       </c>
       <c r="E329" t="str">
-        <v>12690</v>
+        <v>7990</v>
       </c>
       <c r="F329" t="str">
         <v>Por peso</v>
@@ -6981,19 +6981,19 @@
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>408850</v>
+        <v>408083</v>
       </c>
       <c r="B330" t="str">
-        <v>BABY BACK RIBS AMERICANO SUPERCERDO</v>
+        <v>GUATA PRIMERA PROCARNE</v>
       </c>
       <c r="C330" t="str">
         <v/>
       </c>
       <c r="D330" t="str">
-        <v>8850</v>
+        <v>8083</v>
       </c>
       <c r="E330" t="str">
-        <v>14290</v>
+        <v>4990</v>
       </c>
       <c r="F330" t="str">
         <v>Por peso</v>
@@ -7001,19 +7001,19 @@
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>409777</v>
+        <v>408084</v>
       </c>
       <c r="B331" t="str">
-        <v>CHULETA VETADA SUPERCERDO</v>
+        <v>CRIADILLA DE VACUNO PROCARNE</v>
       </c>
       <c r="C331" t="str">
         <v/>
       </c>
       <c r="D331" t="str">
-        <v>9777</v>
+        <v>8084</v>
       </c>
       <c r="E331" t="str">
-        <v>7990</v>
+        <v>4290</v>
       </c>
       <c r="F331" t="str">
         <v>Por peso</v>
@@ -7021,19 +7021,19 @@
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>408083</v>
+        <v>408088</v>
       </c>
       <c r="B332" t="str">
-        <v>GUATA PRIMERA PROCARNE</v>
+        <v>LENGUA VACUNO CONG PROCARNE</v>
       </c>
       <c r="C332" t="str">
         <v/>
       </c>
       <c r="D332" t="str">
-        <v>8083</v>
+        <v>8088</v>
       </c>
       <c r="E332" t="str">
-        <v>4990</v>
+        <v>19990</v>
       </c>
       <c r="F332" t="str">
         <v>Por peso</v>
@@ -7041,19 +7041,19 @@
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>408084</v>
+        <v>408089</v>
       </c>
       <c r="B333" t="str">
-        <v>CRIADILLA DE VACUNO PROCARNE</v>
+        <v>RINON VACUNO CONG VACIO PROCARNE</v>
       </c>
       <c r="C333" t="str">
         <v/>
       </c>
       <c r="D333" t="str">
-        <v>8084</v>
+        <v>8089</v>
       </c>
       <c r="E333" t="str">
-        <v>4290</v>
+        <v>6990</v>
       </c>
       <c r="F333" t="str">
         <v>Por peso</v>
@@ -7061,19 +7061,19 @@
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>408088</v>
+        <v>409090</v>
       </c>
       <c r="B334" t="str">
-        <v>LENGUA VACUNO CONG PROCARNE</v>
+        <v>V. PUNTA PICANA BRASIL KG</v>
       </c>
       <c r="C334" t="str">
         <v/>
       </c>
       <c r="D334" t="str">
-        <v>8088</v>
+        <v>9090</v>
       </c>
       <c r="E334" t="str">
-        <v>19990</v>
+        <v>10790</v>
       </c>
       <c r="F334" t="str">
         <v>Por peso</v>
@@ -7081,19 +7081,19 @@
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>408089</v>
+        <v>408990</v>
       </c>
       <c r="B335" t="str">
-        <v>RINON VACUNO CONG VACIO PROCARNE</v>
+        <v>V. PALANCA BRASIL KG</v>
       </c>
       <c r="C335" t="str">
         <v/>
       </c>
       <c r="D335" t="str">
-        <v>8089</v>
+        <v>8990</v>
       </c>
       <c r="E335" t="str">
-        <v>6990</v>
+        <v>12290</v>
       </c>
       <c r="F335" t="str">
         <v>Por peso</v>
@@ -7101,19 +7101,19 @@
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>409090</v>
+        <v>408090</v>
       </c>
       <c r="B336" t="str">
-        <v>V. PUNTA PICANA BRASIL KG</v>
+        <v>PECHUGA POLLO DESH CONG MAR</v>
       </c>
       <c r="C336" t="str">
         <v/>
       </c>
       <c r="D336" t="str">
-        <v>9090</v>
+        <v>8090</v>
       </c>
       <c r="E336" t="str">
-        <v>10790</v>
+        <v>6990</v>
       </c>
       <c r="F336" t="str">
         <v>Por peso</v>
@@ -7121,19 +7121,19 @@
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>408990</v>
+        <v>408091</v>
       </c>
       <c r="B337" t="str">
-        <v>V. PALANCA BRASIL KG</v>
+        <v>COSTILLAR CRIOLLO CONG. VALLED-</v>
       </c>
       <c r="C337" t="str">
         <v/>
       </c>
       <c r="D337" t="str">
-        <v>8990</v>
+        <v>8091</v>
       </c>
       <c r="E337" t="str">
-        <v>12290</v>
+        <v>9990</v>
       </c>
       <c r="F337" t="str">
         <v>Por peso</v>
@@ -7141,39 +7141,39 @@
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>408090</v>
+        <v>408092</v>
       </c>
       <c r="B338" t="str">
-        <v>PECHUGA POLLO DESH CONG MAR</v>
+        <v>CHURRASCO CAJA 3.5KG FLOW PACK</v>
       </c>
       <c r="C338" t="str">
         <v/>
       </c>
       <c r="D338" t="str">
-        <v>8090</v>
+        <v>8092</v>
       </c>
       <c r="E338" t="str">
-        <v>6990</v>
+        <v>29990</v>
       </c>
       <c r="F338" t="str">
-        <v>Por peso</v>
+        <v>Por cantidad</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>408091</v>
+        <v>408093</v>
       </c>
       <c r="B339" t="str">
-        <v>COSTILLAR CRIOLLO CONG. VALLED-</v>
+        <v>TRUTRO ALA POLLO CONG SUPERPOLLO</v>
       </c>
       <c r="C339" t="str">
         <v/>
       </c>
       <c r="D339" t="str">
-        <v>8091</v>
+        <v>8093</v>
       </c>
       <c r="E339" t="str">
-        <v>9990</v>
+        <v>5490</v>
       </c>
       <c r="F339" t="str">
         <v>Por peso</v>
@@ -7181,87 +7181,47 @@
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>408092</v>
+        <v>404042</v>
       </c>
       <c r="B340" t="str">
-        <v>CHURRASCO CAJA 3.5KG FLOW PACK</v>
+        <v>COSTILLAR CHILENO SUPERCERDO.</v>
       </c>
       <c r="C340" t="str">
         <v/>
       </c>
       <c r="D340" t="str">
-        <v>8092</v>
+        <v>4042</v>
       </c>
       <c r="E340" t="str">
-        <v>29990</v>
+        <v>12690</v>
       </c>
       <c r="F340" t="str">
-        <v>Por cantidad</v>
+        <v>Por peso</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>408093</v>
+        <v>401728</v>
       </c>
       <c r="B341" t="str">
-        <v>TRUTRO ALA POLLO CONG SUPERPOLLO</v>
+        <v>SOBRE-HUACHA EQUINO KG</v>
       </c>
       <c r="C341" t="str">
         <v/>
       </c>
       <c r="D341" t="str">
-        <v>8093</v>
+        <v>1728</v>
       </c>
       <c r="E341" t="str">
-        <v>5490</v>
+        <v>8290</v>
       </c>
       <c r="F341" t="str">
-        <v>Por peso</v>
-      </c>
-    </row>
-    <row r="342">
-      <c r="A342" t="str">
-        <v>404042</v>
-      </c>
-      <c r="B342" t="str">
-        <v>COSTILLAR CHILENO SUPERCERDO.</v>
-      </c>
-      <c r="C342" t="str">
-        <v/>
-      </c>
-      <c r="D342" t="str">
-        <v>4042</v>
-      </c>
-      <c r="E342" t="str">
-        <v>12690</v>
-      </c>
-      <c r="F342" t="str">
-        <v>Por peso</v>
-      </c>
-    </row>
-    <row r="343">
-      <c r="A343" t="str">
-        <v>401728</v>
-      </c>
-      <c r="B343" t="str">
-        <v>SOBRE-HUACHA EQUINO KG</v>
-      </c>
-      <c r="C343" t="str">
-        <v/>
-      </c>
-      <c r="D343" t="str">
-        <v>1728</v>
-      </c>
-      <c r="E343" t="str">
-        <v>8290</v>
-      </c>
-      <c r="F343" t="str">
         <v>Por peso</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F343"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F341"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/MaestraPLU_Carniceria.xlsx
+++ b/MaestraPLU_Carniceria.xlsx
@@ -1413,7 +1413,7 @@
         <v>2066</v>
       </c>
       <c r="E51" t="str">
-        <v>7990</v>
+        <v>6990</v>
       </c>
       <c r="F51" t="str">
         <v>Por peso</v>
@@ -1533,7 +1533,7 @@
         <v>2302</v>
       </c>
       <c r="E57" t="str">
-        <v>4690</v>
+        <v>3690</v>
       </c>
       <c r="F57" t="str">
         <v>Por peso</v>
@@ -1653,7 +1653,7 @@
         <v>2106</v>
       </c>
       <c r="E63" t="str">
-        <v>10290</v>
+        <v>9990</v>
       </c>
       <c r="F63" t="str">
         <v>Por peso</v>
@@ -1753,7 +1753,7 @@
         <v>2057</v>
       </c>
       <c r="E68" t="str">
-        <v>4690</v>
+        <v>3990</v>
       </c>
       <c r="F68" t="str">
         <v>Por peso</v>
@@ -6313,7 +6313,7 @@
         <v>9778</v>
       </c>
       <c r="E296" t="str">
-        <v>6490</v>
+        <v>6290</v>
       </c>
       <c r="F296" t="str">
         <v>Por peso</v>
@@ -6533,7 +6533,7 @@
         <v>3456</v>
       </c>
       <c r="E307" t="str">
-        <v>5690</v>
+        <v>4990</v>
       </c>
       <c r="F307" t="str">
         <v>Por peso</v>
@@ -6813,7 +6813,7 @@
         <v>3032</v>
       </c>
       <c r="E321" t="str">
-        <v>8290</v>
+        <v>7690</v>
       </c>
       <c r="F321" t="str">
         <v>Por peso</v>
@@ -6973,7 +6973,7 @@
         <v>9777</v>
       </c>
       <c r="E329" t="str">
-        <v>7990</v>
+        <v>6690</v>
       </c>
       <c r="F329" t="str">
         <v>Por peso</v>

--- a/MaestraPLU_Carniceria.xlsx
+++ b/MaestraPLU_Carniceria.xlsx
@@ -1033,7 +1033,7 @@
         <v>1095</v>
       </c>
       <c r="E32" t="str">
-        <v>11000</v>
+        <v>10600</v>
       </c>
       <c r="F32" t="str">
         <v>Por peso</v>
@@ -1073,7 +1073,7 @@
         <v>1544</v>
       </c>
       <c r="E34" t="str">
-        <v>11000</v>
+        <v>10600</v>
       </c>
       <c r="F34" t="str">
         <v>Por peso</v>
@@ -1113,7 +1113,7 @@
         <v>1184</v>
       </c>
       <c r="E36" t="str">
-        <v>11000</v>
+        <v>10600</v>
       </c>
       <c r="F36" t="str">
         <v>Por peso</v>

--- a/MaestraPLU_Carniceria.xlsx
+++ b/MaestraPLU_Carniceria.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F341"/>
+  <dimension ref="A1:F343"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1393,7 +1393,7 @@
         <v>2021</v>
       </c>
       <c r="E50" t="str">
-        <v>7690</v>
+        <v>6990</v>
       </c>
       <c r="F50" t="str">
         <v>Por peso</v>
@@ -1453,7 +1453,7 @@
         <v>2046</v>
       </c>
       <c r="E53" t="str">
-        <v>1690</v>
+        <v>1490</v>
       </c>
       <c r="F53" t="str">
         <v>Por peso</v>
@@ -1633,7 +1633,7 @@
         <v>2041</v>
       </c>
       <c r="E62" t="str">
-        <v>1290</v>
+        <v>990</v>
       </c>
       <c r="F62" t="str">
         <v>Por peso</v>
@@ -1673,7 +1673,7 @@
         <v>2034</v>
       </c>
       <c r="E64" t="str">
-        <v>7690</v>
+        <v>7290</v>
       </c>
       <c r="F64" t="str">
         <v>Por peso</v>
@@ -1693,7 +1693,7 @@
         <v>2025</v>
       </c>
       <c r="E65" t="str">
-        <v>6690</v>
+        <v>6290</v>
       </c>
       <c r="F65" t="str">
         <v>Por peso</v>
@@ -1733,7 +1733,7 @@
         <v>2027</v>
       </c>
       <c r="E67" t="str">
-        <v>6290</v>
+        <v>5990</v>
       </c>
       <c r="F67" t="str">
         <v>Por peso</v>
@@ -1813,7 +1813,7 @@
         <v>2569</v>
       </c>
       <c r="E71" t="str">
-        <v>9990</v>
+        <v>9490</v>
       </c>
       <c r="F71" t="str">
         <v>Por peso</v>
@@ -1913,7 +1913,7 @@
         <v>3157</v>
       </c>
       <c r="E76" t="str">
-        <v>8290</v>
+        <v>7990</v>
       </c>
       <c r="F76" t="str">
         <v>Por peso</v>
@@ -1933,7 +1933,7 @@
         <v>2239</v>
       </c>
       <c r="E77" t="str">
-        <v>1690</v>
+        <v>1490</v>
       </c>
       <c r="F77" t="str">
         <v>Por peso</v>
@@ -1953,7 +1953,7 @@
         <v>2022</v>
       </c>
       <c r="E78" t="str">
-        <v>1690</v>
+        <v>1490</v>
       </c>
       <c r="F78" t="str">
         <v>Por peso</v>
@@ -2013,7 +2013,7 @@
         <v>2322</v>
       </c>
       <c r="E81" t="str">
-        <v>8290</v>
+        <v>7690</v>
       </c>
       <c r="F81" t="str">
         <v>Por peso</v>
@@ -2033,7 +2033,7 @@
         <v>2320</v>
       </c>
       <c r="E82" t="str">
-        <v>5490</v>
+        <v>4990</v>
       </c>
       <c r="F82" t="str">
         <v>Por peso</v>
@@ -2053,7 +2053,7 @@
         <v>2321</v>
       </c>
       <c r="E83" t="str">
-        <v>7990</v>
+        <v>8290</v>
       </c>
       <c r="F83" t="str">
         <v>Por peso</v>
@@ -2453,7 +2453,7 @@
         <v>2436</v>
       </c>
       <c r="E103" t="str">
-        <v>2990</v>
+        <v>3090</v>
       </c>
       <c r="F103" t="str">
         <v>Por peso</v>
@@ -2473,7 +2473,7 @@
         <v>2075</v>
       </c>
       <c r="E104" t="str">
-        <v>2990</v>
+        <v>2790</v>
       </c>
       <c r="F104" t="str">
         <v>Por peso</v>
@@ -2693,7 +2693,7 @@
         <v>3218</v>
       </c>
       <c r="E115" t="str">
-        <v>7590</v>
+        <v>7490</v>
       </c>
       <c r="F115" t="str">
         <v>Por peso</v>
@@ -2813,7 +2813,7 @@
         <v>1446</v>
       </c>
       <c r="E121" t="str">
-        <v>1690</v>
+        <v>1990</v>
       </c>
       <c r="F121" t="str">
         <v>Por peso</v>
@@ -2893,7 +2893,7 @@
         <v>3174</v>
       </c>
       <c r="E125" t="str">
-        <v>1690</v>
+        <v>1990</v>
       </c>
       <c r="F125" t="str">
         <v>Por peso</v>
@@ -2973,7 +2973,7 @@
         <v>1616</v>
       </c>
       <c r="E129" t="str">
-        <v>12490</v>
+        <v>11990</v>
       </c>
       <c r="F129" t="str">
         <v>Por peso</v>
@@ -3013,7 +3013,7 @@
         <v>1614</v>
       </c>
       <c r="E131" t="str">
-        <v>11990</v>
+        <v>11690</v>
       </c>
       <c r="F131" t="str">
         <v>Por peso</v>
@@ -3033,7 +3033,7 @@
         <v>1610</v>
       </c>
       <c r="E132" t="str">
-        <v>11990</v>
+        <v>11690</v>
       </c>
       <c r="F132" t="str">
         <v>Por peso</v>
@@ -3073,7 +3073,7 @@
         <v>1602</v>
       </c>
       <c r="E134" t="str">
-        <v>12690</v>
+        <v>11990</v>
       </c>
       <c r="F134" t="str">
         <v>Por peso</v>
@@ -3093,7 +3093,7 @@
         <v>1592</v>
       </c>
       <c r="E135" t="str">
-        <v>10990</v>
+        <v>10690</v>
       </c>
       <c r="F135" t="str">
         <v>Por peso</v>
@@ -3153,7 +3153,7 @@
         <v>1590</v>
       </c>
       <c r="E138" t="str">
-        <v>11990</v>
+        <v>11690</v>
       </c>
       <c r="F138" t="str">
         <v>Por peso</v>
@@ -3193,7 +3193,7 @@
         <v>1574</v>
       </c>
       <c r="E140" t="str">
-        <v>10990</v>
+        <v>10690</v>
       </c>
       <c r="F140" t="str">
         <v>Por peso</v>
@@ -3213,7 +3213,7 @@
         <v>1576</v>
       </c>
       <c r="E141" t="str">
-        <v>11990</v>
+        <v>11690</v>
       </c>
       <c r="F141" t="str">
         <v>Por peso</v>
@@ -3253,7 +3253,7 @@
         <v>1572</v>
       </c>
       <c r="E143" t="str">
-        <v>17990</v>
+        <v>17490</v>
       </c>
       <c r="F143" t="str">
         <v>Por peso</v>
@@ -3273,7 +3273,7 @@
         <v>1564</v>
       </c>
       <c r="E144" t="str">
-        <v>14990</v>
+        <v>14690</v>
       </c>
       <c r="F144" t="str">
         <v>Por peso</v>
@@ -3333,7 +3333,7 @@
         <v>1560</v>
       </c>
       <c r="E147" t="str">
-        <v>11990</v>
+        <v>11690</v>
       </c>
       <c r="F147" t="str">
         <v>Por peso</v>
@@ -3353,7 +3353,7 @@
         <v>1538</v>
       </c>
       <c r="E148" t="str">
-        <v>11990</v>
+        <v>11690</v>
       </c>
       <c r="F148" t="str">
         <v>Por peso</v>
@@ -3373,7 +3373,7 @@
         <v>1537</v>
       </c>
       <c r="E149" t="str">
-        <v>10990</v>
+        <v>10690</v>
       </c>
       <c r="F149" t="str">
         <v>Por peso</v>
@@ -3393,7 +3393,7 @@
         <v>1533</v>
       </c>
       <c r="E150" t="str">
-        <v>12690</v>
+        <v>11990</v>
       </c>
       <c r="F150" t="str">
         <v>Por peso</v>
@@ -3413,7 +3413,7 @@
         <v>1530</v>
       </c>
       <c r="E151" t="str">
-        <v>12490</v>
+        <v>11990</v>
       </c>
       <c r="F151" t="str">
         <v>Por peso</v>
@@ -3433,7 +3433,7 @@
         <v>1528</v>
       </c>
       <c r="E152" t="str">
-        <v>11990</v>
+        <v>11690</v>
       </c>
       <c r="F152" t="str">
         <v>Por peso</v>
@@ -3473,7 +3473,7 @@
         <v>1521</v>
       </c>
       <c r="E154" t="str">
-        <v>17990</v>
+        <v>17490</v>
       </c>
       <c r="F154" t="str">
         <v>Por peso</v>
@@ -3573,7 +3573,7 @@
         <v>1019</v>
       </c>
       <c r="E159" t="str">
-        <v>12000</v>
+        <v>11990</v>
       </c>
       <c r="F159" t="str">
         <v>Por peso</v>
@@ -3593,7 +3593,7 @@
         <v>1441</v>
       </c>
       <c r="E160" t="str">
-        <v>8990</v>
+        <v>9290</v>
       </c>
       <c r="F160" t="str">
         <v>Por peso</v>
@@ -3613,7 +3613,7 @@
         <v>1217</v>
       </c>
       <c r="E161" t="str">
-        <v>13690</v>
+        <v>14490</v>
       </c>
       <c r="F161" t="str">
         <v>Por peso</v>
@@ -3753,7 +3753,7 @@
         <v>1199</v>
       </c>
       <c r="E168" t="str">
-        <v>9690</v>
+        <v>9990</v>
       </c>
       <c r="F168" t="str">
         <v>Por peso</v>
@@ -3853,7 +3853,7 @@
         <v>1108</v>
       </c>
       <c r="E173" t="str">
-        <v>1690</v>
+        <v>1990</v>
       </c>
       <c r="F173" t="str">
         <v>Por peso</v>
@@ -3973,7 +3973,7 @@
         <v>1090</v>
       </c>
       <c r="E179" t="str">
-        <v>7590</v>
+        <v>7490</v>
       </c>
       <c r="F179" t="str">
         <v>Por peso</v>
@@ -4113,7 +4113,7 @@
         <v>1065</v>
       </c>
       <c r="E186" t="str">
-        <v>7590</v>
+        <v>7490</v>
       </c>
       <c r="F186" t="str">
         <v>Por peso</v>
@@ -4153,7 +4153,7 @@
         <v>1069</v>
       </c>
       <c r="E188" t="str">
-        <v>13490</v>
+        <v>13190</v>
       </c>
       <c r="F188" t="str">
         <v>Por peso</v>
@@ -4173,7 +4173,7 @@
         <v>1112</v>
       </c>
       <c r="E189" t="str">
-        <v>12990</v>
+        <v>12490</v>
       </c>
       <c r="F189" t="str">
         <v>Por peso</v>
@@ -4213,7 +4213,7 @@
         <v>1073</v>
       </c>
       <c r="E191" t="str">
-        <v>13490</v>
+        <v>13190</v>
       </c>
       <c r="F191" t="str">
         <v>Por peso</v>
@@ -4233,7 +4233,7 @@
         <v>1033</v>
       </c>
       <c r="E192" t="str">
-        <v>15990</v>
+        <v>15690</v>
       </c>
       <c r="F192" t="str">
         <v>Por peso</v>
@@ -4273,7 +4273,7 @@
         <v>1077</v>
       </c>
       <c r="E194" t="str">
-        <v>12990</v>
+        <v>12490</v>
       </c>
       <c r="F194" t="str">
         <v>Por peso</v>
@@ -4393,7 +4393,7 @@
         <v>1064</v>
       </c>
       <c r="E200" t="str">
-        <v>13490</v>
+        <v>13190</v>
       </c>
       <c r="F200" t="str">
         <v>Por peso</v>
@@ -4413,7 +4413,7 @@
         <v>1093</v>
       </c>
       <c r="E201" t="str">
-        <v>19290</v>
+        <v>18990</v>
       </c>
       <c r="F201" t="str">
         <v>Por peso</v>
@@ -4513,7 +4513,7 @@
         <v>1014</v>
       </c>
       <c r="E206" t="str">
-        <v>18290</v>
+        <v>17990</v>
       </c>
       <c r="F206" t="str">
         <v>Por peso</v>
@@ -4553,7 +4553,7 @@
         <v>1006</v>
       </c>
       <c r="E208" t="str">
-        <v>13490</v>
+        <v>13190</v>
       </c>
       <c r="F208" t="str">
         <v>Por peso</v>
@@ -4593,7 +4593,7 @@
         <v>1002</v>
       </c>
       <c r="E210" t="str">
-        <v>13490</v>
+        <v>13690</v>
       </c>
       <c r="F210" t="str">
         <v>Por peso</v>
@@ -4633,7 +4633,7 @@
         <v>1279</v>
       </c>
       <c r="E212" t="str">
-        <v>14990</v>
+        <v>14690</v>
       </c>
       <c r="F212" t="str">
         <v>Por peso</v>
@@ -4653,7 +4653,7 @@
         <v>1254</v>
       </c>
       <c r="E213" t="str">
-        <v>11990</v>
+        <v>11690</v>
       </c>
       <c r="F213" t="str">
         <v>Por peso</v>
@@ -4713,7 +4713,7 @@
         <v>1288</v>
       </c>
       <c r="E216" t="str">
-        <v>1990</v>
+        <v>2790</v>
       </c>
       <c r="F216" t="str">
         <v>Por peso</v>
@@ -4833,7 +4833,7 @@
         <v>1490</v>
       </c>
       <c r="E222" t="str">
-        <v>11990</v>
+        <v>11690</v>
       </c>
       <c r="F222" t="str">
         <v>Por peso</v>
@@ -4973,7 +4973,7 @@
         <v>3167</v>
       </c>
       <c r="E229" t="str">
-        <v>10990</v>
+        <v>10690</v>
       </c>
       <c r="F229" t="str">
         <v>Por peso</v>
@@ -5013,7 +5013,7 @@
         <v>1402</v>
       </c>
       <c r="E231" t="str">
-        <v>13490</v>
+        <v>12990</v>
       </c>
       <c r="F231" t="str">
         <v>Por peso</v>
@@ -5153,7 +5153,7 @@
         <v>2351</v>
       </c>
       <c r="E238" t="str">
-        <v>3290</v>
+        <v>2990</v>
       </c>
       <c r="F238" t="str">
         <v>Por peso</v>
@@ -5161,19 +5161,19 @@
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>401701</v>
+        <v>401352</v>
       </c>
       <c r="B239" t="str">
-        <v>NOVILLO EN PIE KILO</v>
+        <v>V.COGOTE VACUNO</v>
       </c>
       <c r="C239" t="str">
         <v/>
       </c>
       <c r="D239" t="str">
-        <v>1701</v>
+        <v>1352</v>
       </c>
       <c r="E239" t="str">
-        <v>2850</v>
+        <v>11990</v>
       </c>
       <c r="F239" t="str">
         <v>Por peso</v>
@@ -5181,19 +5181,19 @@
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>401702</v>
+        <v>401701</v>
       </c>
       <c r="B240" t="str">
-        <v>NOVILLO EN PIE</v>
+        <v>NOVILLO EN PIE KILO</v>
       </c>
       <c r="C240" t="str">
         <v/>
       </c>
       <c r="D240" t="str">
-        <v>1702</v>
+        <v>1701</v>
       </c>
       <c r="E240" t="str">
-        <v>2100</v>
+        <v>2850</v>
       </c>
       <c r="F240" t="str">
         <v>Por peso</v>
@@ -5201,19 +5201,19 @@
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>401705</v>
+        <v>401702</v>
       </c>
       <c r="B241" t="str">
-        <v>FILETE DE EQUINO KILO</v>
+        <v>NOVILLO EN PIE</v>
       </c>
       <c r="C241" t="str">
         <v/>
       </c>
       <c r="D241" t="str">
-        <v>1705</v>
+        <v>1702</v>
       </c>
       <c r="E241" t="str">
-        <v>11790</v>
+        <v>2100</v>
       </c>
       <c r="F241" t="str">
         <v>Por peso</v>
@@ -5221,19 +5221,19 @@
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>401706</v>
+        <v>401705</v>
       </c>
       <c r="B242" t="str">
-        <v>LOMO LISO EQUINO KG.</v>
+        <v>FILETE DE EQUINO KILO</v>
       </c>
       <c r="C242" t="str">
         <v/>
       </c>
       <c r="D242" t="str">
-        <v>1706</v>
+        <v>1705</v>
       </c>
       <c r="E242" t="str">
-        <v>11490</v>
+        <v>11790</v>
       </c>
       <c r="F242" t="str">
         <v>Por peso</v>
@@ -5241,19 +5241,19 @@
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>401707</v>
+        <v>401706</v>
       </c>
       <c r="B243" t="str">
-        <v>ASIENTO EQUINO KG.</v>
+        <v>LOMO LISO EQUINO KG.</v>
       </c>
       <c r="C243" t="str">
         <v/>
       </c>
       <c r="D243" t="str">
-        <v>1707</v>
+        <v>1706</v>
       </c>
       <c r="E243" t="str">
-        <v>9990</v>
+        <v>11490</v>
       </c>
       <c r="F243" t="str">
         <v>Por peso</v>
@@ -5261,19 +5261,19 @@
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>401708</v>
+        <v>401707</v>
       </c>
       <c r="B244" t="str">
-        <v>PUNTA PICANA EQUINO KG.</v>
+        <v>ASIENTO EQUINO KG.</v>
       </c>
       <c r="C244" t="str">
         <v/>
       </c>
       <c r="D244" t="str">
-        <v>1708</v>
+        <v>1707</v>
       </c>
       <c r="E244" t="str">
-        <v>7990</v>
+        <v>9990</v>
       </c>
       <c r="F244" t="str">
         <v>Por peso</v>
@@ -5281,19 +5281,19 @@
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>401709</v>
+        <v>401708</v>
       </c>
       <c r="B245" t="str">
-        <v>POLLO GANSO EQUINO KG.</v>
+        <v>PUNTA PICANA EQUINO KG.</v>
       </c>
       <c r="C245" t="str">
         <v/>
       </c>
       <c r="D245" t="str">
-        <v>1709</v>
+        <v>1708</v>
       </c>
       <c r="E245" t="str">
-        <v>8290</v>
+        <v>7990</v>
       </c>
       <c r="F245" t="str">
         <v>Por peso</v>
@@ -5301,16 +5301,16 @@
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>401710</v>
+        <v>401709</v>
       </c>
       <c r="B246" t="str">
-        <v>GANSO EQUINO KG.</v>
+        <v>POLLO GANSO EQUINO KG.</v>
       </c>
       <c r="C246" t="str">
         <v/>
       </c>
       <c r="D246" t="str">
-        <v>1710</v>
+        <v>1709</v>
       </c>
       <c r="E246" t="str">
         <v>8290</v>
@@ -5321,19 +5321,19 @@
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>401711</v>
+        <v>401710</v>
       </c>
       <c r="B247" t="str">
-        <v>PUNTA GANSO EQUINO KG.</v>
+        <v>GANSO EQUINO KG.</v>
       </c>
       <c r="C247" t="str">
         <v/>
       </c>
       <c r="D247" t="str">
-        <v>1711</v>
+        <v>1710</v>
       </c>
       <c r="E247" t="str">
-        <v>7990</v>
+        <v>8290</v>
       </c>
       <c r="F247" t="str">
         <v>Por peso</v>
@@ -5341,19 +5341,19 @@
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>401713</v>
+        <v>401711</v>
       </c>
       <c r="B248" t="str">
-        <v>POSTA NEGRA EQUINO KG.</v>
+        <v>PUNTA GANSO EQUINO KG.</v>
       </c>
       <c r="C248" t="str">
         <v/>
       </c>
       <c r="D248" t="str">
-        <v>1713</v>
+        <v>1711</v>
       </c>
       <c r="E248" t="str">
-        <v>9490</v>
+        <v>7990</v>
       </c>
       <c r="F248" t="str">
         <v>Por peso</v>
@@ -5361,19 +5361,19 @@
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>401714</v>
+        <v>401713</v>
       </c>
       <c r="B249" t="str">
-        <v>POSTA ROSADA EQUINO KG</v>
+        <v>POSTA NEGRA EQUINO KG.</v>
       </c>
       <c r="C249" t="str">
         <v/>
       </c>
       <c r="D249" t="str">
-        <v>1714</v>
+        <v>1713</v>
       </c>
       <c r="E249" t="str">
-        <v>9490</v>
+        <v>9290</v>
       </c>
       <c r="F249" t="str">
         <v>Por peso</v>
@@ -5381,19 +5381,19 @@
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>401715</v>
+        <v>401714</v>
       </c>
       <c r="B250" t="str">
-        <v>PALANCA EQUINO KG.</v>
+        <v>POSTA ROSADA EQUINO KG</v>
       </c>
       <c r="C250" t="str">
         <v/>
       </c>
       <c r="D250" t="str">
-        <v>1715</v>
+        <v>1714</v>
       </c>
       <c r="E250" t="str">
-        <v>8290</v>
+        <v>9290</v>
       </c>
       <c r="F250" t="str">
         <v>Por peso</v>
@@ -5401,19 +5401,19 @@
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>401716</v>
+        <v>401715</v>
       </c>
       <c r="B251" t="str">
-        <v>ABASTERO EQUINO KG.</v>
+        <v>PALANCA EQUINO KG.</v>
       </c>
       <c r="C251" t="str">
         <v/>
       </c>
       <c r="D251" t="str">
-        <v>1716</v>
+        <v>1715</v>
       </c>
       <c r="E251" t="str">
-        <v>7990</v>
+        <v>8290</v>
       </c>
       <c r="F251" t="str">
         <v>Por peso</v>
@@ -5421,19 +5421,19 @@
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>401717</v>
+        <v>401716</v>
       </c>
       <c r="B252" t="str">
-        <v>TAPABARRIGA EQUINO KG.</v>
+        <v>ABASTERO EQUINO KG.</v>
       </c>
       <c r="C252" t="str">
         <v/>
       </c>
       <c r="D252" t="str">
-        <v>1717</v>
+        <v>1716</v>
       </c>
       <c r="E252" t="str">
-        <v>6690</v>
+        <v>7990</v>
       </c>
       <c r="F252" t="str">
         <v>Por peso</v>
@@ -5441,16 +5441,16 @@
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>401718</v>
+        <v>401717</v>
       </c>
       <c r="B253" t="str">
-        <v>POLLO BARRIGA EQUINO KG.</v>
+        <v>TAPABARRIGA EQUINO KG.</v>
       </c>
       <c r="C253" t="str">
         <v/>
       </c>
       <c r="D253" t="str">
-        <v>1718</v>
+        <v>1717</v>
       </c>
       <c r="E253" t="str">
         <v>6690</v>
@@ -5461,19 +5461,19 @@
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>401719</v>
+        <v>401718</v>
       </c>
       <c r="B254" t="str">
-        <v>LOMO VETADO EQUINO KG.</v>
+        <v>POLLO BARRIGA EQUINO KG.</v>
       </c>
       <c r="C254" t="str">
         <v/>
       </c>
       <c r="D254" t="str">
-        <v>1719</v>
+        <v>1718</v>
       </c>
       <c r="E254" t="str">
-        <v>11490</v>
+        <v>6690</v>
       </c>
       <c r="F254" t="str">
         <v>Por peso</v>
@@ -5481,19 +5481,19 @@
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>401720</v>
+        <v>401719</v>
       </c>
       <c r="B255" t="str">
-        <v>POSTA PALETA EQUINO KG.</v>
+        <v>LOMO VETADO EQUINO KG.</v>
       </c>
       <c r="C255" t="str">
         <v/>
       </c>
       <c r="D255" t="str">
-        <v>1720</v>
+        <v>1719</v>
       </c>
       <c r="E255" t="str">
-        <v>9490</v>
+        <v>11490</v>
       </c>
       <c r="F255" t="str">
         <v>Por peso</v>
@@ -5501,19 +5501,19 @@
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>401721</v>
+        <v>401720</v>
       </c>
       <c r="B256" t="str">
-        <v>PUNTA PALETA EQUINO KG.</v>
+        <v>POSTA PALETA EQUINO KG.</v>
       </c>
       <c r="C256" t="str">
         <v/>
       </c>
       <c r="D256" t="str">
-        <v>1721</v>
+        <v>1720</v>
       </c>
       <c r="E256" t="str">
-        <v>7990</v>
+        <v>9290</v>
       </c>
       <c r="F256" t="str">
         <v>Por peso</v>
@@ -5521,19 +5521,19 @@
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>401722</v>
+        <v>401721</v>
       </c>
       <c r="B257" t="str">
-        <v>CHOCLILLO EQUINO KG.</v>
+        <v>PUNTA PALETA EQUINO KG.</v>
       </c>
       <c r="C257" t="str">
         <v/>
       </c>
       <c r="D257" t="str">
-        <v>1722</v>
+        <v>1721</v>
       </c>
       <c r="E257" t="str">
-        <v>8490</v>
+        <v>7990</v>
       </c>
       <c r="F257" t="str">
         <v>Por peso</v>
@@ -5541,16 +5541,16 @@
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>401723</v>
+        <v>401722</v>
       </c>
       <c r="B258" t="str">
-        <v>ASADO CARNICERO EQUINO KG.</v>
+        <v>CHOCLILLO EQUINO KG.</v>
       </c>
       <c r="C258" t="str">
         <v/>
       </c>
       <c r="D258" t="str">
-        <v>1723</v>
+        <v>1722</v>
       </c>
       <c r="E258" t="str">
         <v>8490</v>
@@ -5561,16 +5561,16 @@
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>401724</v>
+        <v>401723</v>
       </c>
       <c r="B259" t="str">
-        <v>PLATEADA EQUINO KG.</v>
+        <v>ASADO CARNICERO EQUINO KG.</v>
       </c>
       <c r="C259" t="str">
         <v/>
       </c>
       <c r="D259" t="str">
-        <v>1724</v>
+        <v>1723</v>
       </c>
       <c r="E259" t="str">
         <v>8490</v>
@@ -5581,19 +5581,19 @@
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>401725</v>
+        <v>401724</v>
       </c>
       <c r="B260" t="str">
-        <v>SOBRECOSTILLA EQUINO KG.</v>
+        <v>PLATEADA EQUINO KG.</v>
       </c>
       <c r="C260" t="str">
         <v/>
       </c>
       <c r="D260" t="str">
-        <v>1725</v>
+        <v>1724</v>
       </c>
       <c r="E260" t="str">
-        <v>8490</v>
+        <v>8290</v>
       </c>
       <c r="F260" t="str">
         <v>Por peso</v>
@@ -5601,16 +5601,16 @@
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>401726</v>
+        <v>401725</v>
       </c>
       <c r="B261" t="str">
-        <v>HUACHALOMO EQUINO KG.</v>
+        <v>SOBRECOSTILLA EQUINO KG.</v>
       </c>
       <c r="C261" t="str">
         <v/>
       </c>
       <c r="D261" t="str">
-        <v>1726</v>
+        <v>1725</v>
       </c>
       <c r="E261" t="str">
         <v>8490</v>
@@ -5621,19 +5621,19 @@
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>401727</v>
+        <v>401726</v>
       </c>
       <c r="B262" t="str">
-        <v>TAPAPECHO EQUINO KG.</v>
+        <v>HUACHALOMO EQUINO KG.</v>
       </c>
       <c r="C262" t="str">
         <v/>
       </c>
       <c r="D262" t="str">
-        <v>1727</v>
+        <v>1726</v>
       </c>
       <c r="E262" t="str">
-        <v>5690</v>
+        <v>8490</v>
       </c>
       <c r="F262" t="str">
         <v>Por peso</v>
@@ -5641,19 +5641,19 @@
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>401729</v>
+        <v>401727</v>
       </c>
       <c r="B263" t="str">
-        <v>ENTRANAS EQUINO KG.</v>
+        <v>TAPAPECHO EQUINO KG.</v>
       </c>
       <c r="C263" t="str">
         <v/>
       </c>
       <c r="D263" t="str">
-        <v>1729</v>
+        <v>1727</v>
       </c>
       <c r="E263" t="str">
-        <v>6490</v>
+        <v>5690</v>
       </c>
       <c r="F263" t="str">
         <v>Por peso</v>
@@ -5661,19 +5661,19 @@
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>401730</v>
+        <v>401729</v>
       </c>
       <c r="B264" t="str">
-        <v>MALAYA EQUINO KG.</v>
+        <v>ENTRANAS EQUINO KG.</v>
       </c>
       <c r="C264" t="str">
         <v/>
       </c>
       <c r="D264" t="str">
-        <v>1730</v>
+        <v>1729</v>
       </c>
       <c r="E264" t="str">
-        <v>2690</v>
+        <v>6490</v>
       </c>
       <c r="F264" t="str">
         <v>Por peso</v>
@@ -5681,19 +5681,19 @@
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>401731</v>
+        <v>401730</v>
       </c>
       <c r="B265" t="str">
-        <v>CARNE MOLIDA CTE EQUINO KG.</v>
+        <v>MALAYA EQUINO KG.</v>
       </c>
       <c r="C265" t="str">
         <v/>
       </c>
       <c r="D265" t="str">
-        <v>1731</v>
+        <v>1730</v>
       </c>
       <c r="E265" t="str">
-        <v>7290</v>
+        <v>2690</v>
       </c>
       <c r="F265" t="str">
         <v>Por peso</v>
@@ -5701,19 +5701,19 @@
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>401732</v>
+        <v>401731</v>
       </c>
       <c r="B266" t="str">
-        <v>CARNE MOLIDA ESPEC. EQUINO KG.</v>
+        <v>CARNE MOLIDA CTE EQUINO KG.</v>
       </c>
       <c r="C266" t="str">
         <v/>
       </c>
       <c r="D266" t="str">
-        <v>1732</v>
+        <v>1731</v>
       </c>
       <c r="E266" t="str">
-        <v>8290</v>
+        <v>7290</v>
       </c>
       <c r="F266" t="str">
         <v>Por peso</v>
@@ -5721,19 +5721,19 @@
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>401733</v>
+        <v>401732</v>
       </c>
       <c r="B267" t="str">
-        <v>ASADO DE TIRA EQUINO KG.</v>
+        <v>CARNE MOLIDA ESPEC. EQUINO KG.</v>
       </c>
       <c r="C267" t="str">
         <v/>
       </c>
       <c r="D267" t="str">
-        <v>1733</v>
+        <v>1732</v>
       </c>
       <c r="E267" t="str">
-        <v>3990</v>
+        <v>8290</v>
       </c>
       <c r="F267" t="str">
         <v>Por peso</v>
@@ -5741,19 +5741,19 @@
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>401734</v>
+        <v>401733</v>
       </c>
       <c r="B268" t="str">
-        <v>OSOBUCO MANO PIERNA EQUINO KG.</v>
+        <v>ASADO DE TIRA EQUINO KG.</v>
       </c>
       <c r="C268" t="str">
         <v/>
       </c>
       <c r="D268" t="str">
-        <v>1734</v>
+        <v>1733</v>
       </c>
       <c r="E268" t="str">
-        <v>2990</v>
+        <v>3990</v>
       </c>
       <c r="F268" t="str">
         <v>Por peso</v>
@@ -5761,16 +5761,16 @@
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>401735</v>
+        <v>401734</v>
       </c>
       <c r="B269" t="str">
-        <v>LAGARTO MANO EQUINO KG.</v>
+        <v>OSOBUCO MANO PIERNA EQUINO KG.</v>
       </c>
       <c r="C269" t="str">
         <v/>
       </c>
       <c r="D269" t="str">
-        <v>1735</v>
+        <v>1734</v>
       </c>
       <c r="E269" t="str">
         <v>2990</v>
@@ -5781,19 +5781,19 @@
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>401736</v>
+        <v>401735</v>
       </c>
       <c r="B270" t="str">
-        <v>ALETILLA EQUINO KG.</v>
+        <v>LAGARTO MANO EQUINO KG.</v>
       </c>
       <c r="C270" t="str">
         <v/>
       </c>
       <c r="D270" t="str">
-        <v>1736</v>
+        <v>1735</v>
       </c>
       <c r="E270" t="str">
-        <v>1990</v>
+        <v>2990</v>
       </c>
       <c r="F270" t="str">
         <v>Por peso</v>
@@ -5801,16 +5801,16 @@
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>401737</v>
+        <v>401736</v>
       </c>
       <c r="B271" t="str">
-        <v>COLUDA EQUINO KG.</v>
+        <v>ALETILLA EQUINO KG.</v>
       </c>
       <c r="C271" t="str">
         <v/>
       </c>
       <c r="D271" t="str">
-        <v>1737</v>
+        <v>1736</v>
       </c>
       <c r="E271" t="str">
         <v>1990</v>
@@ -5821,19 +5821,19 @@
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>401738</v>
+        <v>401737</v>
       </c>
       <c r="B272" t="str">
-        <v>HUESO CARNUDO EQUINO KG.</v>
+        <v>COLUDA EQUINO KG.</v>
       </c>
       <c r="C272" t="str">
         <v/>
       </c>
       <c r="D272" t="str">
-        <v>1738</v>
+        <v>1737</v>
       </c>
       <c r="E272" t="str">
-        <v>1790</v>
+        <v>1990</v>
       </c>
       <c r="F272" t="str">
         <v>Por peso</v>
@@ -5841,19 +5841,19 @@
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>401739</v>
+        <v>401738</v>
       </c>
       <c r="B273" t="str">
-        <v>HUESO PELADO EQUINO KG.</v>
+        <v>HUESO CARNUDO EQUINO KG.</v>
       </c>
       <c r="C273" t="str">
         <v/>
       </c>
       <c r="D273" t="str">
-        <v>1739</v>
+        <v>1738</v>
       </c>
       <c r="E273" t="str">
-        <v>890</v>
+        <v>1990</v>
       </c>
       <c r="F273" t="str">
         <v>Por peso</v>
@@ -5861,19 +5861,19 @@
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>401740</v>
+        <v>401739</v>
       </c>
       <c r="B274" t="str">
-        <v>COLA EQUINO KG.</v>
+        <v>HUESO PELADO EQUINO KG.</v>
       </c>
       <c r="C274" t="str">
         <v/>
       </c>
       <c r="D274" t="str">
-        <v>1740</v>
+        <v>1739</v>
       </c>
       <c r="E274" t="str">
-        <v>790</v>
+        <v>990</v>
       </c>
       <c r="F274" t="str">
         <v>Por peso</v>
@@ -5881,19 +5881,19 @@
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>401741</v>
+        <v>401740</v>
       </c>
       <c r="B275" t="str">
-        <v>GRASA EQUINO KG.</v>
+        <v>COLA EQUINO KG.</v>
       </c>
       <c r="C275" t="str">
         <v/>
       </c>
       <c r="D275" t="str">
-        <v>1741</v>
+        <v>1740</v>
       </c>
       <c r="E275" t="str">
-        <v>690</v>
+        <v>890</v>
       </c>
       <c r="F275" t="str">
         <v>Por peso</v>
@@ -5901,19 +5901,19 @@
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>401535</v>
+        <v>401741</v>
       </c>
       <c r="B276" t="str">
-        <v>TRUTRO CUARTO USA KILO</v>
+        <v>GRASA EQUINO KG.</v>
       </c>
       <c r="C276" t="str">
         <v/>
       </c>
       <c r="D276" t="str">
-        <v>1535</v>
+        <v>1741</v>
       </c>
       <c r="E276" t="str">
-        <v>2390</v>
+        <v>890</v>
       </c>
       <c r="F276" t="str">
         <v>Por peso</v>
@@ -5921,19 +5921,19 @@
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>401751</v>
+        <v>401535</v>
       </c>
       <c r="B277" t="str">
-        <v>GUATA EQUINO KG</v>
+        <v>TRUTRO CUARTO USA KILO</v>
       </c>
       <c r="C277" t="str">
         <v/>
       </c>
       <c r="D277" t="str">
-        <v>1751</v>
+        <v>1535</v>
       </c>
       <c r="E277" t="str">
-        <v>990</v>
+        <v>2390</v>
       </c>
       <c r="F277" t="str">
         <v>Por peso</v>
@@ -5941,19 +5941,19 @@
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>401752</v>
+        <v>401751</v>
       </c>
       <c r="B278" t="str">
-        <v>HIGADO EQUINO</v>
+        <v>GUATA EQUINO KG</v>
       </c>
       <c r="C278" t="str">
         <v/>
       </c>
       <c r="D278" t="str">
-        <v>1752</v>
+        <v>1751</v>
       </c>
       <c r="E278" t="str">
-        <v>2490</v>
+        <v>990</v>
       </c>
       <c r="F278" t="str">
         <v>Por peso</v>
@@ -5961,19 +5961,19 @@
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>401753</v>
+        <v>401752</v>
       </c>
       <c r="B279" t="str">
-        <v>CORAZON EQUINO</v>
+        <v>HIGADO EQUINO</v>
       </c>
       <c r="C279" t="str">
         <v/>
       </c>
       <c r="D279" t="str">
-        <v>1753</v>
+        <v>1752</v>
       </c>
       <c r="E279" t="str">
-        <v>990</v>
+        <v>2490</v>
       </c>
       <c r="F279" t="str">
         <v>Por peso</v>
@@ -5981,19 +5981,19 @@
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>401754</v>
+        <v>401753</v>
       </c>
       <c r="B280" t="str">
-        <v>LENGUA EQUINO</v>
+        <v>CORAZON EQUINO</v>
       </c>
       <c r="C280" t="str">
         <v/>
       </c>
       <c r="D280" t="str">
-        <v>1754</v>
+        <v>1753</v>
       </c>
       <c r="E280" t="str">
-        <v>1990</v>
+        <v>990</v>
       </c>
       <c r="F280" t="str">
         <v>Por peso</v>
@@ -6001,19 +6001,19 @@
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>401755</v>
+        <v>401754</v>
       </c>
       <c r="B281" t="str">
-        <v>CHUNCHULE EQUINO</v>
+        <v>LENGUA EQUINO</v>
       </c>
       <c r="C281" t="str">
         <v/>
       </c>
       <c r="D281" t="str">
-        <v>1755</v>
+        <v>1754</v>
       </c>
       <c r="E281" t="str">
-        <v>1490</v>
+        <v>1990</v>
       </c>
       <c r="F281" t="str">
         <v>Por peso</v>
@@ -6021,19 +6021,19 @@
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>401756</v>
+        <v>401755</v>
       </c>
       <c r="B282" t="str">
-        <v>CHARCHAS EQUINO</v>
+        <v>CHUNCHULE EQUINO</v>
       </c>
       <c r="C282" t="str">
         <v/>
       </c>
       <c r="D282" t="str">
-        <v>1756</v>
+        <v>1755</v>
       </c>
       <c r="E282" t="str">
-        <v>1190</v>
+        <v>1490</v>
       </c>
       <c r="F282" t="str">
         <v>Por peso</v>
@@ -6041,19 +6041,19 @@
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>401757</v>
+        <v>401756</v>
       </c>
       <c r="B283" t="str">
-        <v>RINONES EQUINO</v>
+        <v>CHARCHAS EQUINO</v>
       </c>
       <c r="C283" t="str">
         <v/>
       </c>
       <c r="D283" t="str">
-        <v>1757</v>
+        <v>1756</v>
       </c>
       <c r="E283" t="str">
-        <v>990</v>
+        <v>1190</v>
       </c>
       <c r="F283" t="str">
         <v>Por peso</v>
@@ -6061,19 +6061,19 @@
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>401696</v>
+        <v>401757</v>
       </c>
       <c r="B284" t="str">
-        <v>V.POSTA PALETA BRA PORC.</v>
+        <v>RINONES EQUINO</v>
       </c>
       <c r="C284" t="str">
         <v/>
       </c>
       <c r="D284" t="str">
-        <v>1696</v>
+        <v>1757</v>
       </c>
       <c r="E284" t="str">
-        <v>9690</v>
+        <v>990</v>
       </c>
       <c r="F284" t="str">
         <v>Por peso</v>
@@ -6081,19 +6081,19 @@
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>401094</v>
+        <v>401696</v>
       </c>
       <c r="B285" t="str">
-        <v>V.SOBREC-HUACHA</v>
+        <v>V.POSTA PALETA BRA PORC.</v>
       </c>
       <c r="C285" t="str">
         <v/>
       </c>
       <c r="D285" t="str">
-        <v>1094</v>
+        <v>1696</v>
       </c>
       <c r="E285" t="str">
-        <v>13490</v>
+        <v>9690</v>
       </c>
       <c r="F285" t="str">
         <v>Por peso</v>
@@ -6101,19 +6101,19 @@
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>402589</v>
+        <v>405865</v>
       </c>
       <c r="B286" t="str">
-        <v>TRUTRO ENTERO CONG.AGROSUPER</v>
+        <v>U.COGOTE NACIONAL</v>
       </c>
       <c r="C286" t="str">
         <v/>
       </c>
       <c r="D286" t="str">
-        <v>2589</v>
+        <v>5865</v>
       </c>
       <c r="E286" t="str">
-        <v>4990</v>
+        <v>11990</v>
       </c>
       <c r="F286" t="str">
         <v>Por peso</v>
@@ -6121,19 +6121,19 @@
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>402580</v>
+        <v>401094</v>
       </c>
       <c r="B287" t="str">
-        <v>CHULETA VETADA IMP C</v>
+        <v>V.SOBREC-HUACHA</v>
       </c>
       <c r="C287" t="str">
         <v/>
       </c>
       <c r="D287" t="str">
-        <v>2580</v>
+        <v>1094</v>
       </c>
       <c r="E287" t="str">
-        <v>5290</v>
+        <v>13190</v>
       </c>
       <c r="F287" t="str">
         <v>Por peso</v>
@@ -6141,19 +6141,19 @@
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>401396</v>
+        <v>402589</v>
       </c>
       <c r="B288" t="str">
-        <v>C.LAGARTO MANO</v>
+        <v>TRUTRO ENTERO CONG.AGROSUPER</v>
       </c>
       <c r="C288" t="str">
         <v/>
       </c>
       <c r="D288" t="str">
-        <v>1396</v>
+        <v>2589</v>
       </c>
       <c r="E288" t="str">
-        <v>9690</v>
+        <v>4990</v>
       </c>
       <c r="F288" t="str">
         <v>Por peso</v>
@@ -6161,19 +6161,19 @@
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>401390</v>
+        <v>402580</v>
       </c>
       <c r="B289" t="str">
-        <v>C.PUNTA PALETA</v>
+        <v>CHULETA VETADA IMP C</v>
       </c>
       <c r="C289" t="str">
         <v/>
       </c>
       <c r="D289" t="str">
-        <v>1390</v>
+        <v>2580</v>
       </c>
       <c r="E289" t="str">
-        <v>11990</v>
+        <v>5290</v>
       </c>
       <c r="F289" t="str">
         <v>Por peso</v>
@@ -6181,19 +6181,19 @@
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>402565</v>
+        <v>401396</v>
       </c>
       <c r="B290" t="str">
-        <v>VACUNO DESPOSTADO V</v>
+        <v>C.LAGARTO MANO</v>
       </c>
       <c r="C290" t="str">
         <v/>
       </c>
       <c r="D290" t="str">
-        <v>2565</v>
+        <v>1396</v>
       </c>
       <c r="E290" t="str">
-        <v>4500</v>
+        <v>9690</v>
       </c>
       <c r="F290" t="str">
         <v>Por peso</v>
@@ -6201,19 +6201,19 @@
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>402940</v>
+        <v>401390</v>
       </c>
       <c r="B291" t="str">
-        <v>TRUTRO PARRILERO PAVO ARIZTIA</v>
+        <v>C.PUNTA PALETA</v>
       </c>
       <c r="C291" t="str">
         <v/>
       </c>
       <c r="D291" t="str">
-        <v>2940</v>
+        <v>1390</v>
       </c>
       <c r="E291" t="str">
-        <v>10490</v>
+        <v>11690</v>
       </c>
       <c r="F291" t="str">
         <v>Por peso</v>
@@ -6221,19 +6221,19 @@
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>402858</v>
+        <v>402565</v>
       </c>
       <c r="B292" t="str">
-        <v>C.SOBRECOST HUACHALOMO CORTE AMERICANO</v>
+        <v>VACUNO DESPOSTADO V</v>
       </c>
       <c r="C292" t="str">
         <v/>
       </c>
       <c r="D292" t="str">
-        <v>2858</v>
+        <v>2565</v>
       </c>
       <c r="E292" t="str">
-        <v>12990</v>
+        <v>4500</v>
       </c>
       <c r="F292" t="str">
         <v>Por peso</v>
@@ -6241,99 +6241,99 @@
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>403559</v>
+        <v>402940</v>
       </c>
       <c r="B293" t="str">
-        <v>TRUTRO CUARTO BRASIL CAJA 10 KG</v>
+        <v>TRUTRO PARRILERO PAVO ARIZTIA</v>
       </c>
       <c r="C293" t="str">
         <v/>
       </c>
       <c r="D293" t="str">
-        <v>3559</v>
+        <v>2940</v>
       </c>
       <c r="E293" t="str">
-        <v>23990</v>
+        <v>10490</v>
       </c>
       <c r="F293" t="str">
-        <v>Por cantidad</v>
+        <v>Por peso</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>403566</v>
+        <v>402858</v>
       </c>
       <c r="B294" t="str">
-        <v>TRUTRO CUARTO BLOCK CAJA 15</v>
+        <v>C.SOBRECOST HUACHALOMO CORTE AMERICANO</v>
       </c>
       <c r="C294" t="str">
         <v/>
       </c>
       <c r="D294" t="str">
-        <v>3566</v>
+        <v>2858</v>
       </c>
       <c r="E294" t="str">
-        <v>37990</v>
+        <v>12990</v>
       </c>
       <c r="F294" t="str">
-        <v>Por cantidad</v>
+        <v>Por peso</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>405099</v>
+        <v>403559</v>
       </c>
       <c r="B295" t="str">
-        <v>CORAZON CONG DESGRASADO</v>
+        <v>TRUTRO CUARTO BRASIL CAJA 10 KG</v>
       </c>
       <c r="C295" t="str">
         <v/>
       </c>
       <c r="D295" t="str">
-        <v>5099</v>
+        <v>3559</v>
       </c>
       <c r="E295" t="str">
-        <v>4990</v>
+        <v>23990</v>
       </c>
       <c r="F295" t="str">
-        <v>Por peso</v>
+        <v>Por cantidad</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>409778</v>
+        <v>403566</v>
       </c>
       <c r="B296" t="str">
-        <v>CHULETA CENTRO SUPERCERDO</v>
+        <v>TRUTRO CUARTO BLOCK CAJA 15</v>
       </c>
       <c r="C296" t="str">
         <v/>
       </c>
       <c r="D296" t="str">
-        <v>9778</v>
+        <v>3566</v>
       </c>
       <c r="E296" t="str">
-        <v>6290</v>
+        <v>37990</v>
       </c>
       <c r="F296" t="str">
-        <v>Por peso</v>
+        <v>Por cantidad</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>405662</v>
+        <v>405099</v>
       </c>
       <c r="B297" t="str">
-        <v>ENTRECOT EQUINO VARA</v>
+        <v>CORAZON CONG DESGRASADO</v>
       </c>
       <c r="C297" t="str">
         <v/>
       </c>
       <c r="D297" t="str">
-        <v>5662</v>
+        <v>5099</v>
       </c>
       <c r="E297" t="str">
-        <v>9990</v>
+        <v>4990</v>
       </c>
       <c r="F297" t="str">
         <v>Por peso</v>
@@ -6341,19 +6341,19 @@
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>408079</v>
+        <v>409778</v>
       </c>
       <c r="B298" t="str">
-        <v>HIGADO IMP CONG</v>
+        <v>CHULETA CENTRO SUPERCERDO</v>
       </c>
       <c r="C298" t="str">
         <v/>
       </c>
       <c r="D298" t="str">
-        <v>8079</v>
+        <v>9778</v>
       </c>
       <c r="E298" t="str">
-        <v>4990</v>
+        <v>6290</v>
       </c>
       <c r="F298" t="str">
         <v>Por peso</v>
@@ -6361,19 +6361,19 @@
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>408081</v>
+        <v>405662</v>
       </c>
       <c r="B299" t="str">
-        <v>HUESO COGOTE TIPO V PROCARNE</v>
+        <v>ENTRECOT EQUINO VARA</v>
       </c>
       <c r="C299" t="str">
         <v/>
       </c>
       <c r="D299" t="str">
-        <v>8081</v>
+        <v>5662</v>
       </c>
       <c r="E299" t="str">
-        <v>6990</v>
+        <v>9990</v>
       </c>
       <c r="F299" t="str">
         <v>Por peso</v>
@@ -6381,16 +6381,16 @@
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>409782</v>
+        <v>408079</v>
       </c>
       <c r="B300" t="str">
-        <v>GUATA SEGUNDA PROCAR</v>
+        <v>HIGADO IMP CONG</v>
       </c>
       <c r="C300" t="str">
         <v/>
       </c>
       <c r="D300" t="str">
-        <v>9782</v>
+        <v>8079</v>
       </c>
       <c r="E300" t="str">
         <v>4990</v>
@@ -6401,19 +6401,19 @@
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>409783</v>
+        <v>408081</v>
       </c>
       <c r="B301" t="str">
-        <v>COLA DE VACUNO PROCARNE</v>
+        <v>HUESO COGOTE TIPO V PROCARNE</v>
       </c>
       <c r="C301" t="str">
         <v/>
       </c>
       <c r="D301" t="str">
-        <v>9783</v>
+        <v>8081</v>
       </c>
       <c r="E301" t="str">
-        <v>3990</v>
+        <v>6990</v>
       </c>
       <c r="F301" t="str">
         <v>Por peso</v>
@@ -6421,19 +6421,19 @@
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>409791</v>
+        <v>409782</v>
       </c>
       <c r="B302" t="str">
-        <v>HIGADO PROCARNE</v>
+        <v>GUATA SEGUNDA PROCAR</v>
       </c>
       <c r="C302" t="str">
         <v/>
       </c>
       <c r="D302" t="str">
-        <v>9791</v>
+        <v>9782</v>
       </c>
       <c r="E302" t="str">
-        <v>4290</v>
+        <v>4990</v>
       </c>
       <c r="F302" t="str">
         <v>Por peso</v>
@@ -6441,19 +6441,19 @@
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>405878</v>
+        <v>409783</v>
       </c>
       <c r="B303" t="str">
-        <v>V.ENTRANA VACUNO IMP PARAGUAY</v>
+        <v>COLA DE VACUNO PROCARNE</v>
       </c>
       <c r="C303" t="str">
         <v/>
       </c>
       <c r="D303" t="str">
-        <v>5878</v>
+        <v>9783</v>
       </c>
       <c r="E303" t="str">
-        <v>18990</v>
+        <v>3990</v>
       </c>
       <c r="F303" t="str">
         <v>Por peso</v>
@@ -6461,19 +6461,19 @@
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>405879</v>
+        <v>409791</v>
       </c>
       <c r="B304" t="str">
-        <v>PATAS DE POLLO CONG ARIZTIA</v>
+        <v>HIGADO PROCARNE</v>
       </c>
       <c r="C304" t="str">
         <v/>
       </c>
       <c r="D304" t="str">
-        <v>5879</v>
+        <v>9791</v>
       </c>
       <c r="E304" t="str">
-        <v>2990</v>
+        <v>4290</v>
       </c>
       <c r="F304" t="str">
         <v>Por peso</v>
@@ -6481,19 +6481,19 @@
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>409100</v>
+        <v>405878</v>
       </c>
       <c r="B305" t="str">
-        <v>C.MANTA TRASERA CONG</v>
+        <v>V.ENTRANA VACUNO IMP PARAGUAY</v>
       </c>
       <c r="C305" t="str">
         <v/>
       </c>
       <c r="D305" t="str">
-        <v>9100</v>
+        <v>5878</v>
       </c>
       <c r="E305" t="str">
-        <v>7290</v>
+        <v>18990</v>
       </c>
       <c r="F305" t="str">
         <v>Por peso</v>
@@ -6501,19 +6501,19 @@
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>405893</v>
+        <v>405879</v>
       </c>
       <c r="B306" t="str">
-        <v>COGOTE EQUINO VARA</v>
+        <v>PATAS DE POLLO CONG ARIZTIA</v>
       </c>
       <c r="C306" t="str">
         <v/>
       </c>
       <c r="D306" t="str">
-        <v>5893</v>
+        <v>5879</v>
       </c>
       <c r="E306" t="str">
-        <v>2490</v>
+        <v>2990</v>
       </c>
       <c r="F306" t="str">
         <v>Por peso</v>
@@ -6521,19 +6521,19 @@
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>403456</v>
+        <v>409100</v>
       </c>
       <c r="B307" t="str">
-        <v>TRUTRO CUARTO AGROSUPER</v>
+        <v>C.MANTA TRASERA CONG</v>
       </c>
       <c r="C307" t="str">
         <v/>
       </c>
       <c r="D307" t="str">
-        <v>3456</v>
+        <v>9100</v>
       </c>
       <c r="E307" t="str">
-        <v>4990</v>
+        <v>7290</v>
       </c>
       <c r="F307" t="str">
         <v>Por peso</v>
@@ -6541,19 +6541,19 @@
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>402130</v>
+        <v>405893</v>
       </c>
       <c r="B308" t="str">
-        <v>V.COSTILLA ARQUEADA</v>
+        <v>COGOTE EQUINO VARA</v>
       </c>
       <c r="C308" t="str">
         <v/>
       </c>
       <c r="D308" t="str">
-        <v>2130</v>
+        <v>5893</v>
       </c>
       <c r="E308" t="str">
-        <v>4990</v>
+        <v>2490</v>
       </c>
       <c r="F308" t="str">
         <v>Por peso</v>
@@ -6561,16 +6561,16 @@
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>404021</v>
+        <v>403456</v>
       </c>
       <c r="B309" t="str">
-        <v>C.COSTILLA ARQUEADA</v>
+        <v>TRUTRO CUARTO AGROSUPER</v>
       </c>
       <c r="C309" t="str">
         <v/>
       </c>
       <c r="D309" t="str">
-        <v>4021</v>
+        <v>3456</v>
       </c>
       <c r="E309" t="str">
         <v>4990</v>
@@ -6581,19 +6581,19 @@
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>404789</v>
+        <v>402130</v>
       </c>
       <c r="B310" t="str">
-        <v>COSTILLAR AHUMADO DON RODRIGO</v>
+        <v>V.COSTILLA ARQUEADA</v>
       </c>
       <c r="C310" t="str">
         <v/>
       </c>
       <c r="D310" t="str">
-        <v>4789</v>
+        <v>2130</v>
       </c>
       <c r="E310" t="str">
-        <v>8990</v>
+        <v>4990</v>
       </c>
       <c r="F310" t="str">
         <v>Por peso</v>
@@ -6601,19 +6601,19 @@
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>404880</v>
+        <v>404021</v>
       </c>
       <c r="B311" t="str">
-        <v>COSTILLAR ALINADO DON RODRIGO</v>
+        <v>C.COSTILLA ARQUEADA</v>
       </c>
       <c r="C311" t="str">
         <v/>
       </c>
       <c r="D311" t="str">
-        <v>4880</v>
+        <v>4021</v>
       </c>
       <c r="E311" t="str">
-        <v>8990</v>
+        <v>4990</v>
       </c>
       <c r="F311" t="str">
         <v>Por peso</v>
@@ -6621,16 +6621,16 @@
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>402352</v>
+        <v>404789</v>
       </c>
       <c r="B312" t="str">
-        <v>COSTILLAR BARBECUE DON RODRIGO</v>
+        <v>COSTILLAR AHUMADO DON RODRIGO</v>
       </c>
       <c r="C312" t="str">
         <v/>
       </c>
       <c r="D312" t="str">
-        <v>2352</v>
+        <v>4789</v>
       </c>
       <c r="E312" t="str">
         <v>8990</v>
@@ -6641,19 +6641,19 @@
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>408780</v>
+        <v>404880</v>
       </c>
       <c r="B313" t="str">
-        <v>COSTILLAR CRIOLLO COOK AND FUN</v>
+        <v>COSTILLAR ALINADO DON RODRIGO</v>
       </c>
       <c r="C313" t="str">
         <v/>
       </c>
       <c r="D313" t="str">
-        <v>8780</v>
+        <v>4880</v>
       </c>
       <c r="E313" t="str">
-        <v>8490</v>
+        <v>8990</v>
       </c>
       <c r="F313" t="str">
         <v>Por peso</v>
@@ -6661,19 +6661,19 @@
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>408781</v>
+        <v>402352</v>
       </c>
       <c r="B314" t="str">
-        <v>COSTILLAR NATURAL COOK-FUN</v>
+        <v>COSTILLAR BARBECUE DON RODRIGO</v>
       </c>
       <c r="C314" t="str">
         <v/>
       </c>
       <c r="D314" t="str">
-        <v>8781</v>
+        <v>2352</v>
       </c>
       <c r="E314" t="str">
-        <v>8490</v>
+        <v>8990</v>
       </c>
       <c r="F314" t="str">
         <v>Por peso</v>
@@ -6681,19 +6681,19 @@
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>403231</v>
+        <v>408780</v>
       </c>
       <c r="B315" t="str">
-        <v>ALA PUCHERO SUPERPOLLO KG</v>
+        <v>COSTILLAR CRIOLLO COOK AND FUN</v>
       </c>
       <c r="C315" t="str">
         <v/>
       </c>
       <c r="D315" t="str">
-        <v>3231</v>
+        <v>8780</v>
       </c>
       <c r="E315" t="str">
-        <v>3490</v>
+        <v>8490</v>
       </c>
       <c r="F315" t="str">
         <v>Por peso</v>
@@ -6701,19 +6701,19 @@
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>400610</v>
+        <v>408781</v>
       </c>
       <c r="B316" t="str">
-        <v>TRUTRO CORTO POLLO BAND. H-50 SUPER</v>
+        <v>COSTILLAR NATURAL COOK-FUN</v>
       </c>
       <c r="C316" t="str">
         <v/>
       </c>
       <c r="D316" t="str">
-        <v>0610</v>
+        <v>8781</v>
       </c>
       <c r="E316" t="str">
-        <v>5490</v>
+        <v>8490</v>
       </c>
       <c r="F316" t="str">
         <v>Por peso</v>
@@ -6721,19 +6721,19 @@
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>401355</v>
+        <v>403231</v>
       </c>
       <c r="B317" t="str">
-        <v>V.ASIENTO BRASIL VACIO IMP ENTERO</v>
+        <v>ALA PUCHERO SUPERPOLLO KG</v>
       </c>
       <c r="C317" t="str">
         <v/>
       </c>
       <c r="D317" t="str">
-        <v>1355</v>
+        <v>3231</v>
       </c>
       <c r="E317" t="str">
-        <v>12990</v>
+        <v>3490</v>
       </c>
       <c r="F317" t="str">
         <v>Por peso</v>
@@ -6741,19 +6741,19 @@
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>408180</v>
+        <v>400610</v>
       </c>
       <c r="B318" t="str">
-        <v>PECHUGA BANDEJA ENTERA KG SUPERPOLLO</v>
+        <v>TRUTRO CORTO POLLO BAND. H-50 SUPER</v>
       </c>
       <c r="C318" t="str">
         <v/>
       </c>
       <c r="D318" t="str">
-        <v>8180</v>
+        <v>0610</v>
       </c>
       <c r="E318" t="str">
-        <v>6990</v>
+        <v>5490</v>
       </c>
       <c r="F318" t="str">
         <v>Por peso</v>
@@ -6761,19 +6761,19 @@
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>403201</v>
+        <v>401355</v>
       </c>
       <c r="B319" t="str">
-        <v>COGOTE PAVO CONG ARIZTIA</v>
+        <v>V.ASIENTO BRASIL VACIO IMP ENTERO</v>
       </c>
       <c r="C319" t="str">
         <v/>
       </c>
       <c r="D319" t="str">
-        <v>3201</v>
+        <v>1355</v>
       </c>
       <c r="E319" t="str">
-        <v>5490</v>
+        <v>12990</v>
       </c>
       <c r="F319" t="str">
         <v>Por peso</v>
@@ -6781,19 +6781,19 @@
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>406678</v>
+        <v>408180</v>
       </c>
       <c r="B320" t="str">
-        <v>PATAS POLLO IQF GRANEL SUPERPOLLO</v>
+        <v>PECHUGA BANDEJA ENTERA KG SUPERPOLLO</v>
       </c>
       <c r="C320" t="str">
         <v/>
       </c>
       <c r="D320" t="str">
-        <v>6678</v>
+        <v>8180</v>
       </c>
       <c r="E320" t="str">
-        <v>1690</v>
+        <v>6990</v>
       </c>
       <c r="F320" t="str">
         <v>Por peso</v>
@@ -6801,19 +6801,19 @@
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>403032</v>
+        <v>403201</v>
       </c>
       <c r="B321" t="str">
-        <v>PULPA PIERNA 57 SUPERCERDO</v>
+        <v>COGOTE PAVO CONG ARIZTIA</v>
       </c>
       <c r="C321" t="str">
         <v/>
       </c>
       <c r="D321" t="str">
-        <v>3032</v>
+        <v>3201</v>
       </c>
       <c r="E321" t="str">
-        <v>7690</v>
+        <v>5490</v>
       </c>
       <c r="F321" t="str">
         <v>Por peso</v>
@@ -6821,19 +6821,19 @@
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>407002</v>
+        <v>406678</v>
       </c>
       <c r="B322" t="str">
-        <v>COSTILLAR 75 SUPERCERDO</v>
+        <v>PATAS POLLO IQF GRANEL SUPERPOLLO</v>
       </c>
       <c r="C322" t="str">
         <v/>
       </c>
       <c r="D322" t="str">
-        <v>7002</v>
+        <v>6678</v>
       </c>
       <c r="E322" t="str">
-        <v>10990</v>
+        <v>1690</v>
       </c>
       <c r="F322" t="str">
         <v>Por peso</v>
@@ -6841,19 +6841,19 @@
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>407983</v>
+        <v>403032</v>
       </c>
       <c r="B323" t="str">
-        <v>PANA POLLO DON POLLO</v>
+        <v>PULPA PIERNA 57 SUPERCERDO</v>
       </c>
       <c r="C323" t="str">
         <v/>
       </c>
       <c r="D323" t="str">
-        <v>7983</v>
+        <v>3032</v>
       </c>
       <c r="E323" t="str">
-        <v>2990</v>
+        <v>7690</v>
       </c>
       <c r="F323" t="str">
         <v>Por peso</v>
@@ -6861,19 +6861,19 @@
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>407981</v>
+        <v>407002</v>
       </c>
       <c r="B324" t="str">
-        <v>GARRAS O PATAS POLLO DON POLLO</v>
+        <v>COSTILLAR 75 SUPERCERDO</v>
       </c>
       <c r="C324" t="str">
         <v/>
       </c>
       <c r="D324" t="str">
-        <v>7981</v>
+        <v>7002</v>
       </c>
       <c r="E324" t="str">
-        <v>1490</v>
+        <v>10990</v>
       </c>
       <c r="F324" t="str">
         <v>Por peso</v>
@@ -6881,19 +6881,19 @@
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>407980</v>
+        <v>407983</v>
       </c>
       <c r="B325" t="str">
-        <v>CONTRE POLLO DON POLLO</v>
+        <v>PANA POLLO DON POLLO</v>
       </c>
       <c r="C325" t="str">
         <v/>
       </c>
       <c r="D325" t="str">
-        <v>7980</v>
+        <v>7983</v>
       </c>
       <c r="E325" t="str">
-        <v>3690</v>
+        <v>2990</v>
       </c>
       <c r="F325" t="str">
         <v>Por peso</v>
@@ -6901,19 +6901,19 @@
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>402450</v>
+        <v>407981</v>
       </c>
       <c r="B326" t="str">
-        <v>COGOTE POLLO DON POLLO</v>
+        <v>GARRAS O PATAS POLLO DON POLLO</v>
       </c>
       <c r="C326" t="str">
         <v/>
       </c>
       <c r="D326" t="str">
-        <v>2450</v>
+        <v>7981</v>
       </c>
       <c r="E326" t="str">
-        <v>1290</v>
+        <v>1490</v>
       </c>
       <c r="F326" t="str">
         <v>Por peso</v>
@@ -6921,19 +6921,19 @@
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>404041</v>
+        <v>407980</v>
       </c>
       <c r="B327" t="str">
-        <v>COSTILLAR TRADICIONAL SUPERCERDO.</v>
+        <v>CONTRE POLLO DON POLLO</v>
       </c>
       <c r="C327" t="str">
         <v/>
       </c>
       <c r="D327" t="str">
-        <v>4041</v>
+        <v>7980</v>
       </c>
       <c r="E327" t="str">
-        <v>12690</v>
+        <v>3690</v>
       </c>
       <c r="F327" t="str">
         <v>Por peso</v>
@@ -6941,19 +6941,19 @@
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>408850</v>
+        <v>402450</v>
       </c>
       <c r="B328" t="str">
-        <v>BABY BACK RIBS AMERICANO SUPERCERDO</v>
+        <v>COGOTE POLLO DON POLLO</v>
       </c>
       <c r="C328" t="str">
         <v/>
       </c>
       <c r="D328" t="str">
-        <v>8850</v>
+        <v>2450</v>
       </c>
       <c r="E328" t="str">
-        <v>14290</v>
+        <v>1290</v>
       </c>
       <c r="F328" t="str">
         <v>Por peso</v>
@@ -6961,19 +6961,19 @@
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>409777</v>
+        <v>404041</v>
       </c>
       <c r="B329" t="str">
-        <v>CHULETA VETADA SUPERCERDO</v>
+        <v>COSTILLAR TRADICIONAL SUPERCERDO.</v>
       </c>
       <c r="C329" t="str">
         <v/>
       </c>
       <c r="D329" t="str">
-        <v>9777</v>
+        <v>4041</v>
       </c>
       <c r="E329" t="str">
-        <v>6690</v>
+        <v>12690</v>
       </c>
       <c r="F329" t="str">
         <v>Por peso</v>
@@ -6981,19 +6981,19 @@
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>408083</v>
+        <v>408850</v>
       </c>
       <c r="B330" t="str">
-        <v>GUATA PRIMERA PROCARNE</v>
+        <v>BABY BACK RIBS AMERICANO SUPERCERDO</v>
       </c>
       <c r="C330" t="str">
         <v/>
       </c>
       <c r="D330" t="str">
-        <v>8083</v>
+        <v>8850</v>
       </c>
       <c r="E330" t="str">
-        <v>4990</v>
+        <v>14290</v>
       </c>
       <c r="F330" t="str">
         <v>Por peso</v>
@@ -7001,19 +7001,19 @@
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>408084</v>
+        <v>409777</v>
       </c>
       <c r="B331" t="str">
-        <v>CRIADILLA DE VACUNO PROCARNE</v>
+        <v>CHULETA VETADA SUPERCERDO</v>
       </c>
       <c r="C331" t="str">
         <v/>
       </c>
       <c r="D331" t="str">
-        <v>8084</v>
+        <v>9777</v>
       </c>
       <c r="E331" t="str">
-        <v>4290</v>
+        <v>6690</v>
       </c>
       <c r="F331" t="str">
         <v>Por peso</v>
@@ -7021,19 +7021,19 @@
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>408088</v>
+        <v>408083</v>
       </c>
       <c r="B332" t="str">
-        <v>LENGUA VACUNO CONG PROCARNE</v>
+        <v>GUATA PRIMERA PROCARNE</v>
       </c>
       <c r="C332" t="str">
         <v/>
       </c>
       <c r="D332" t="str">
-        <v>8088</v>
+        <v>8083</v>
       </c>
       <c r="E332" t="str">
-        <v>19990</v>
+        <v>4990</v>
       </c>
       <c r="F332" t="str">
         <v>Por peso</v>
@@ -7041,19 +7041,19 @@
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>408089</v>
+        <v>408084</v>
       </c>
       <c r="B333" t="str">
-        <v>RINON VACUNO CONG VACIO PROCARNE</v>
+        <v>CRIADILLA DE VACUNO PROCARNE</v>
       </c>
       <c r="C333" t="str">
         <v/>
       </c>
       <c r="D333" t="str">
-        <v>8089</v>
+        <v>8084</v>
       </c>
       <c r="E333" t="str">
-        <v>6990</v>
+        <v>4290</v>
       </c>
       <c r="F333" t="str">
         <v>Por peso</v>
@@ -7061,19 +7061,19 @@
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>409090</v>
+        <v>408088</v>
       </c>
       <c r="B334" t="str">
-        <v>V. PUNTA PICANA BRASIL KG</v>
+        <v>LENGUA VACUNO CONG PROCARNE</v>
       </c>
       <c r="C334" t="str">
         <v/>
       </c>
       <c r="D334" t="str">
-        <v>9090</v>
+        <v>8088</v>
       </c>
       <c r="E334" t="str">
-        <v>10790</v>
+        <v>19990</v>
       </c>
       <c r="F334" t="str">
         <v>Por peso</v>
@@ -7081,19 +7081,19 @@
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>408990</v>
+        <v>408089</v>
       </c>
       <c r="B335" t="str">
-        <v>V. PALANCA BRASIL KG</v>
+        <v>RINON VACUNO CONG VACIO PROCARNE</v>
       </c>
       <c r="C335" t="str">
         <v/>
       </c>
       <c r="D335" t="str">
-        <v>8990</v>
+        <v>8089</v>
       </c>
       <c r="E335" t="str">
-        <v>12290</v>
+        <v>6990</v>
       </c>
       <c r="F335" t="str">
         <v>Por peso</v>
@@ -7101,19 +7101,19 @@
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>408090</v>
+        <v>409090</v>
       </c>
       <c r="B336" t="str">
-        <v>PECHUGA POLLO DESH CONG MAR</v>
+        <v>V. PUNTA PICANA BRASIL KG</v>
       </c>
       <c r="C336" t="str">
         <v/>
       </c>
       <c r="D336" t="str">
-        <v>8090</v>
+        <v>9090</v>
       </c>
       <c r="E336" t="str">
-        <v>6990</v>
+        <v>10790</v>
       </c>
       <c r="F336" t="str">
         <v>Por peso</v>
@@ -7121,19 +7121,19 @@
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>408091</v>
+        <v>408990</v>
       </c>
       <c r="B337" t="str">
-        <v>COSTILLAR CRIOLLO CONG. VALLED-</v>
+        <v>V. PALANCA BRASIL KG</v>
       </c>
       <c r="C337" t="str">
         <v/>
       </c>
       <c r="D337" t="str">
-        <v>8091</v>
+        <v>8990</v>
       </c>
       <c r="E337" t="str">
-        <v>9990</v>
+        <v>12290</v>
       </c>
       <c r="F337" t="str">
         <v>Por peso</v>
@@ -7141,39 +7141,39 @@
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>408092</v>
+        <v>408090</v>
       </c>
       <c r="B338" t="str">
-        <v>CHURRASCO CAJA 3.5KG FLOW PACK</v>
+        <v>PECHUGA POLLO DESH CONG MAR</v>
       </c>
       <c r="C338" t="str">
         <v/>
       </c>
       <c r="D338" t="str">
-        <v>8092</v>
+        <v>8090</v>
       </c>
       <c r="E338" t="str">
-        <v>29990</v>
+        <v>6990</v>
       </c>
       <c r="F338" t="str">
-        <v>Por cantidad</v>
+        <v>Por peso</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>408093</v>
+        <v>408091</v>
       </c>
       <c r="B339" t="str">
-        <v>TRUTRO ALA POLLO CONG SUPERPOLLO</v>
+        <v>COSTILLAR CRIOLLO CONG. VALLED-</v>
       </c>
       <c r="C339" t="str">
         <v/>
       </c>
       <c r="D339" t="str">
-        <v>8093</v>
+        <v>8091</v>
       </c>
       <c r="E339" t="str">
-        <v>5490</v>
+        <v>9990</v>
       </c>
       <c r="F339" t="str">
         <v>Por peso</v>
@@ -7181,47 +7181,87 @@
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>404042</v>
+        <v>408092</v>
       </c>
       <c r="B340" t="str">
-        <v>COSTILLAR CHILENO SUPERCERDO.</v>
+        <v>CHURRASCO CAJA 3.5KG FLOW PACK</v>
       </c>
       <c r="C340" t="str">
         <v/>
       </c>
       <c r="D340" t="str">
-        <v>4042</v>
+        <v>8092</v>
       </c>
       <c r="E340" t="str">
-        <v>12690</v>
+        <v>29990</v>
       </c>
       <c r="F340" t="str">
-        <v>Por peso</v>
+        <v>Por cantidad</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="str">
+        <v>408093</v>
+      </c>
+      <c r="B341" t="str">
+        <v>TRUTRO ALA POLLO CONG SUPERPOLLO</v>
+      </c>
+      <c r="C341" t="str">
+        <v/>
+      </c>
+      <c r="D341" t="str">
+        <v>8093</v>
+      </c>
+      <c r="E341" t="str">
+        <v>5490</v>
+      </c>
+      <c r="F341" t="str">
+        <v>Por peso</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="str">
+        <v>404042</v>
+      </c>
+      <c r="B342" t="str">
+        <v>COSTILLAR CHILENO SUPERCERDO.</v>
+      </c>
+      <c r="C342" t="str">
+        <v/>
+      </c>
+      <c r="D342" t="str">
+        <v>4042</v>
+      </c>
+      <c r="E342" t="str">
+        <v>12690</v>
+      </c>
+      <c r="F342" t="str">
+        <v>Por peso</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="str">
         <v>401728</v>
       </c>
-      <c r="B341" t="str">
+      <c r="B343" t="str">
         <v>SOBRE-HUACHA EQUINO KG</v>
       </c>
-      <c r="C341" t="str">
-        <v/>
-      </c>
-      <c r="D341" t="str">
+      <c r="C343" t="str">
+        <v/>
+      </c>
+      <c r="D343" t="str">
         <v>1728</v>
       </c>
-      <c r="E341" t="str">
+      <c r="E343" t="str">
         <v>8290</v>
       </c>
-      <c r="F341" t="str">
+      <c r="F343" t="str">
         <v>Por peso</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F341"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F343"/>
   </ignoredErrors>
 </worksheet>
 </file>